--- a/source/AU/TD_AUv3_Restructure.xlsx
+++ b/source/AU/TD_AUv3_Restructure.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="861">
   <si>
     <t xml:space="preserve">APPN Adelaide University vocabularies</t>
   </si>
@@ -2272,9 +2272,6 @@
   </si>
   <si>
     <t xml:space="preserve">genus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">specie (I know they are the same as ScientificName but I wanted to have this column hereto see if we want to keep just one)</t>
   </si>
   <si>
     <t xml:space="preserve">scientificName</t>
@@ -3959,8 +3956,10 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left/>
-      <right style="dotted"/>
-      <top style="dotted"/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.15"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -3969,15 +3968,6 @@
       <right style="dotted"/>
       <top/>
       <bottom style="dotted"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.15"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -4004,6 +3994,13 @@
     <border diagonalUp="false" diagonalDown="false">
       <left style="dotted"/>
       <right/>
+      <top style="dotted"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="dotted"/>
       <top style="dotted"/>
       <bottom/>
       <diagonal/>
@@ -4154,7 +4151,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="290">
+  <cellXfs count="285">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4487,10 +4484,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="17" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="38" fillId="17" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4499,10 +4492,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="17" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="20" fillId="17" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4515,18 +4504,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="17" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="17" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="17" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="20" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4547,7 +4524,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="20" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="42" fillId="20" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4575,14 +4552,14 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="21" fillId="22" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="21" fillId="22" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="22" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="21" fillId="22" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4591,7 +4568,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="22" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="22" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4599,35 +4576,35 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="21" fillId="22" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="22" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="21" fillId="22" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="22" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="20" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="22" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="22" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="22" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="21" fillId="22" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="22" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="22" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4771,7 +4748,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4783,11 +4760,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="17" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="51" fillId="17" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4815,11 +4792,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="17" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="17" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="17" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4835,11 +4812,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="17" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="17" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="52" fillId="17" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="52" fillId="17" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4851,11 +4828,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="52" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4947,7 +4924,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="29" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="29" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4987,7 +4964,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="31" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="40" fillId="31" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4995,14 +4972,14 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="31" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="31" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="31" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="31" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5075,15 +5052,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="34" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="58" fillId="34" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="58" fillId="34" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5119,11 +5096,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="58" fillId="34" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="58" fillId="34" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5143,7 +5120,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5175,42 +5152,42 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="21" fillId="34" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="34" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="58" fillId="34" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="34" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="34" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="34" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="21" fillId="34" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="34" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="58" fillId="34" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="34" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="34" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="34" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="41" fillId="35" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5219,7 +5196,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="34" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="21" fillId="34" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5239,7 +5216,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="58" fillId="34" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="58" fillId="34" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5259,15 +5236,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="58" fillId="34" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="58" fillId="34" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="58" fillId="34" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="58" fillId="34" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="58" fillId="34" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="58" fillId="34" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5458,37 +5435,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="0e2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="e8e8e8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="e97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="196b24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="0f9ed5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="a02b93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="4ea72e"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="96607d"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -5808,155 +5785,155 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="144" width="28.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="144" width="52.63"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="144" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="139" width="28.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="139" width="52.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="139" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="153" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="189" t="s">
+    <row r="1" s="148" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="184" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="190" t="s">
+      <c r="B1" s="185" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="190" t="s">
+      <c r="C1" s="185" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="186" t="s">
+        <v>633</v>
+      </c>
+      <c r="B2" s="187"/>
+      <c r="C2" s="188" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="191" t="s">
+    <row r="3" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="189" t="s">
         <v>634</v>
       </c>
-      <c r="B2" s="192"/>
-      <c r="C2" s="193" t="s">
+      <c r="B3" s="190"/>
+      <c r="C3" s="188" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="194" t="s">
-        <v>635</v>
-      </c>
-      <c r="B3" s="195"/>
-      <c r="C3" s="193" t="s">
+    <row r="4" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="191" t="s">
+        <v>637</v>
+      </c>
+      <c r="B4" s="187"/>
+      <c r="C4" s="188" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="196" t="s">
+    <row r="5" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="192" t="s">
         <v>638</v>
       </c>
-      <c r="B4" s="192"/>
-      <c r="C4" s="193" t="s">
+      <c r="B5" s="190"/>
+      <c r="C5" s="188" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="197" t="s">
-        <v>639</v>
-      </c>
-      <c r="B5" s="195"/>
-      <c r="C5" s="193" t="s">
+    <row r="6" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="193" t="s">
+        <v>644</v>
+      </c>
+      <c r="B6" s="194"/>
+      <c r="C6" s="195" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="198" t="s">
-        <v>645</v>
-      </c>
-      <c r="B6" s="199"/>
-      <c r="C6" s="200" t="s">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="196" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="201" t="s">
+      <c r="B7" s="196"/>
+      <c r="C7" s="197" t="s">
         <v>659</v>
       </c>
-      <c r="B7" s="201"/>
-      <c r="C7" s="202" t="s">
-        <v>660</v>
-      </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="201"/>
-      <c r="B8" s="201"/>
-      <c r="C8" s="201"/>
+      <c r="A8" s="196"/>
+      <c r="B8" s="196"/>
+      <c r="C8" s="196"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="201"/>
-      <c r="B9" s="201"/>
-      <c r="C9" s="201"/>
+      <c r="A9" s="196"/>
+      <c r="B9" s="196"/>
+      <c r="C9" s="196"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="201"/>
-      <c r="B10" s="201"/>
-      <c r="C10" s="201"/>
+      <c r="A10" s="196"/>
+      <c r="B10" s="196"/>
+      <c r="C10" s="196"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="201"/>
-      <c r="B11" s="201"/>
-      <c r="C11" s="201"/>
+      <c r="A11" s="196"/>
+      <c r="B11" s="196"/>
+      <c r="C11" s="196"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="201"/>
-      <c r="B12" s="201"/>
-      <c r="C12" s="201"/>
+      <c r="A12" s="196"/>
+      <c r="B12" s="196"/>
+      <c r="C12" s="196"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="201"/>
-      <c r="B13" s="201"/>
-      <c r="C13" s="201"/>
+      <c r="A13" s="196"/>
+      <c r="B13" s="196"/>
+      <c r="C13" s="196"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="201"/>
-      <c r="B14" s="201"/>
-      <c r="C14" s="201"/>
+      <c r="A14" s="196"/>
+      <c r="B14" s="196"/>
+      <c r="C14" s="196"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="201"/>
-      <c r="B15" s="201"/>
-      <c r="C15" s="201"/>
+      <c r="A15" s="196"/>
+      <c r="B15" s="196"/>
+      <c r="C15" s="196"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="201"/>
-      <c r="B16" s="201"/>
-      <c r="C16" s="201"/>
+      <c r="A16" s="196"/>
+      <c r="B16" s="196"/>
+      <c r="C16" s="196"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="201"/>
-      <c r="B17" s="201"/>
-      <c r="C17" s="201"/>
+      <c r="A17" s="196"/>
+      <c r="B17" s="196"/>
+      <c r="C17" s="196"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="201"/>
-      <c r="B18" s="201"/>
-      <c r="C18" s="201"/>
+      <c r="A18" s="196"/>
+      <c r="B18" s="196"/>
+      <c r="C18" s="196"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="201"/>
-      <c r="B19" s="201"/>
-      <c r="C19" s="201"/>
+      <c r="A19" s="196"/>
+      <c r="B19" s="196"/>
+      <c r="C19" s="196"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="201"/>
-      <c r="B20" s="201"/>
-      <c r="C20" s="201"/>
+      <c r="A20" s="196"/>
+      <c r="B20" s="196"/>
+      <c r="C20" s="196"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="201"/>
-      <c r="B21" s="201"/>
-      <c r="C21" s="201"/>
+      <c r="A21" s="196"/>
+      <c r="B21" s="196"/>
+      <c r="C21" s="196"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="201"/>
-      <c r="B22" s="201"/>
-      <c r="C22" s="201"/>
+      <c r="A22" s="196"/>
+      <c r="B22" s="196"/>
+      <c r="C22" s="196"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="201"/>
-      <c r="B23" s="201"/>
-      <c r="C23" s="201"/>
+      <c r="A23" s="196"/>
+      <c r="B23" s="196"/>
+      <c r="C23" s="196"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5978,151 +5955,151 @@
   <dimension ref="A1:D1048576"/>
   <sheetFormatPr defaultColWidth="8.55078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="203" width="32.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="203" width="46.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="203" width="52.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="198" width="32.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="198" width="46.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="198" width="52.63"/>
   </cols>
   <sheetData>
-    <row r="1" s="207" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="204" t="s">
+    <row r="1" s="202" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="199" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="205" t="s">
+      <c r="B1" s="200" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="206" t="s">
+      <c r="C1" s="201" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="208" t="s">
-        <v>595</v>
-      </c>
-      <c r="B2" s="209" t="s">
-        <v>595</v>
-      </c>
-      <c r="C2" s="210" t="s">
-        <v>595</v>
+      <c r="A2" s="203" t="s">
+        <v>594</v>
+      </c>
+      <c r="B2" s="204" t="s">
+        <v>594</v>
+      </c>
+      <c r="C2" s="205" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="211" t="s">
-        <v>661</v>
-      </c>
-      <c r="B3" s="212" t="s">
-        <v>601</v>
-      </c>
-      <c r="C3" s="213" t="s">
-        <v>636</v>
+      <c r="A3" s="206" t="s">
+        <v>660</v>
+      </c>
+      <c r="B3" s="207" t="s">
+        <v>600</v>
+      </c>
+      <c r="C3" s="208" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="214"/>
-      <c r="B4" s="214"/>
-      <c r="C4" s="214"/>
-      <c r="D4" s="215"/>
+      <c r="A4" s="209"/>
+      <c r="B4" s="209"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="210"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="214"/>
-      <c r="B5" s="214"/>
-      <c r="C5" s="214"/>
-      <c r="D5" s="215"/>
+      <c r="A5" s="209"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="210"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="214"/>
-      <c r="B6" s="214"/>
-      <c r="C6" s="214"/>
-      <c r="D6" s="215"/>
+      <c r="A6" s="209"/>
+      <c r="B6" s="209"/>
+      <c r="C6" s="209"/>
+      <c r="D6" s="210"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="216"/>
-      <c r="B7" s="216"/>
-      <c r="C7" s="216"/>
+      <c r="A7" s="211"/>
+      <c r="B7" s="211"/>
+      <c r="C7" s="211"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="217"/>
-      <c r="B8" s="217"/>
-      <c r="C8" s="217"/>
+      <c r="A8" s="212"/>
+      <c r="B8" s="212"/>
+      <c r="C8" s="212"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="217"/>
-      <c r="B9" s="217"/>
-      <c r="C9" s="217"/>
+      <c r="A9" s="212"/>
+      <c r="B9" s="212"/>
+      <c r="C9" s="212"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="217"/>
-      <c r="B10" s="217"/>
-      <c r="C10" s="217"/>
+      <c r="A10" s="212"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="212"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="217"/>
-      <c r="B11" s="217"/>
-      <c r="C11" s="217"/>
+      <c r="A11" s="212"/>
+      <c r="B11" s="212"/>
+      <c r="C11" s="212"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="217"/>
-      <c r="B12" s="217"/>
-      <c r="C12" s="217"/>
+      <c r="A12" s="212"/>
+      <c r="B12" s="212"/>
+      <c r="C12" s="212"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="217"/>
-      <c r="B13" s="217"/>
-      <c r="C13" s="217"/>
+      <c r="A13" s="212"/>
+      <c r="B13" s="212"/>
+      <c r="C13" s="212"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="217"/>
-      <c r="B14" s="217"/>
-      <c r="C14" s="217"/>
+      <c r="A14" s="212"/>
+      <c r="B14" s="212"/>
+      <c r="C14" s="212"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="217"/>
-      <c r="B15" s="217"/>
-      <c r="C15" s="217"/>
+      <c r="A15" s="212"/>
+      <c r="B15" s="212"/>
+      <c r="C15" s="212"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="217"/>
-      <c r="B16" s="217"/>
-      <c r="C16" s="217"/>
+      <c r="A16" s="212"/>
+      <c r="B16" s="212"/>
+      <c r="C16" s="212"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="217"/>
-      <c r="B17" s="217"/>
-      <c r="C17" s="217"/>
+      <c r="A17" s="212"/>
+      <c r="B17" s="212"/>
+      <c r="C17" s="212"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="217"/>
-      <c r="B18" s="217"/>
-      <c r="C18" s="217"/>
+      <c r="A18" s="212"/>
+      <c r="B18" s="212"/>
+      <c r="C18" s="212"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="217"/>
-      <c r="B19" s="217"/>
-      <c r="C19" s="217"/>
+      <c r="A19" s="212"/>
+      <c r="B19" s="212"/>
+      <c r="C19" s="212"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="217"/>
-      <c r="B20" s="217"/>
-      <c r="C20" s="217"/>
+      <c r="A20" s="212"/>
+      <c r="B20" s="212"/>
+      <c r="C20" s="212"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="217"/>
-      <c r="B21" s="217"/>
-      <c r="C21" s="217"/>
+      <c r="A21" s="212"/>
+      <c r="B21" s="212"/>
+      <c r="C21" s="212"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="217"/>
-      <c r="B22" s="217"/>
-      <c r="C22" s="217"/>
+      <c r="A22" s="212"/>
+      <c r="B22" s="212"/>
+      <c r="C22" s="212"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="217"/>
-      <c r="B23" s="217"/>
-      <c r="C23" s="217"/>
+      <c r="A23" s="212"/>
+      <c r="B23" s="212"/>
+      <c r="C23" s="212"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="217"/>
-      <c r="B24" s="217"/>
-      <c r="C24" s="217"/>
+      <c r="A24" s="212"/>
+      <c r="B24" s="212"/>
+      <c r="C24" s="212"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
@@ -6145,2457 +6122,2457 @@
   <dimension ref="A1:S61"/>
   <sheetFormatPr defaultColWidth="8.55078125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="203" width="23.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="203" width="37.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="203" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="203" width="25.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="203" width="35.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="203" width="33.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="203" width="23.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="203" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="203" width="26.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="203" width="20.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="203" width="28.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="203" width="26.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="203" width="20.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="203" width="32.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="203" width="33.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="203" width="29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="203" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="203" width="26.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="198" width="23.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="198" width="37.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="198" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="198" width="25.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="198" width="35.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="198" width="33.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="198" width="23.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="198" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="198" width="26.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="198" width="20.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="198" width="28.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="198" width="26.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="198" width="20.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="198" width="32.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="198" width="33.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="198" width="29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="198" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="198" width="26.75"/>
   </cols>
   <sheetData>
-    <row r="1" s="229" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="218" t="s">
+    <row r="1" s="224" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="213" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="219" t="s">
+      <c r="B1" s="214" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="220" t="s">
+      <c r="C1" s="215" t="s">
+        <v>661</v>
+      </c>
+      <c r="D1" s="216" t="s">
         <v>662</v>
       </c>
-      <c r="D1" s="221" t="s">
+      <c r="E1" s="217" t="s">
         <v>663</v>
       </c>
-      <c r="E1" s="222" t="s">
+      <c r="F1" s="218" t="s">
         <v>664</v>
       </c>
-      <c r="F1" s="223" t="s">
+      <c r="G1" s="217" t="s">
         <v>665</v>
       </c>
-      <c r="G1" s="222" t="s">
+      <c r="H1" s="216" t="s">
         <v>666</v>
       </c>
-      <c r="H1" s="221" t="s">
+      <c r="I1" s="219" t="s">
         <v>667</v>
       </c>
-      <c r="I1" s="224" t="s">
+      <c r="J1" s="217" t="s">
         <v>668</v>
       </c>
-      <c r="J1" s="222" t="s">
+      <c r="K1" s="216" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="216" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="216" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="215" t="s">
+        <v>591</v>
+      </c>
+      <c r="O1" s="220" t="s">
+        <v>592</v>
+      </c>
+      <c r="P1" s="221" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q1" s="222" t="s">
         <v>669</v>
       </c>
-      <c r="K1" s="221" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" s="221" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="221" t="s">
-        <v>21</v>
-      </c>
-      <c r="N1" s="220" t="s">
-        <v>592</v>
-      </c>
-      <c r="O1" s="225" t="s">
-        <v>593</v>
-      </c>
-      <c r="P1" s="226" t="s">
-        <v>594</v>
-      </c>
-      <c r="Q1" s="227" t="s">
+      <c r="R1" s="213" t="s">
         <v>670</v>
       </c>
-      <c r="R1" s="218" t="s">
+      <c r="S1" s="223"/>
+    </row>
+    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="225" t="s">
         <v>671</v>
       </c>
-      <c r="S1" s="228"/>
-    </row>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="230" t="s">
+      <c r="B2" s="226" t="s">
         <v>672</v>
       </c>
-      <c r="B2" s="231" t="s">
+      <c r="C2" s="227" t="s">
         <v>673</v>
       </c>
-      <c r="C2" s="232" t="s">
+      <c r="D2" s="228" t="s">
         <v>674</v>
       </c>
-      <c r="D2" s="233" t="s">
+      <c r="E2" s="229" t="s">
         <v>675</v>
       </c>
-      <c r="E2" s="234" t="s">
+      <c r="F2" s="229" t="s">
         <v>676</v>
       </c>
-      <c r="F2" s="234" t="s">
+      <c r="G2" s="230" t="s">
         <v>677</v>
       </c>
-      <c r="G2" s="235" t="s">
+      <c r="H2" s="228" t="s">
         <v>678</v>
       </c>
-      <c r="H2" s="233" t="s">
+      <c r="I2" s="231"/>
+      <c r="J2" s="231"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="231"/>
+      <c r="M2" s="231"/>
+      <c r="N2" s="231"/>
+      <c r="O2" s="233"/>
+      <c r="P2" s="233"/>
+      <c r="Q2" s="232" t="s">
         <v>679</v>
       </c>
-      <c r="I2" s="236"/>
-      <c r="J2" s="236"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="236"/>
-      <c r="M2" s="236"/>
-      <c r="N2" s="236"/>
-      <c r="O2" s="238"/>
-      <c r="P2" s="238"/>
-      <c r="Q2" s="237" t="s">
+      <c r="R2" s="231"/>
+      <c r="S2" s="234"/>
+    </row>
+    <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="235" t="s">
         <v>680</v>
       </c>
-      <c r="R2" s="236"/>
-      <c r="S2" s="239"/>
-    </row>
-    <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="240" t="s">
+      <c r="B3" s="236" t="s">
         <v>681</v>
       </c>
-      <c r="B3" s="241" t="s">
+      <c r="C3" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D3" s="228" t="s">
         <v>682</v>
       </c>
-      <c r="C3" s="242" t="s">
+      <c r="E3" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F3" s="228" t="s">
+        <v>684</v>
+      </c>
+      <c r="G3" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I3" s="239"/>
+      <c r="J3" s="239"/>
+      <c r="K3" s="239"/>
+      <c r="L3" s="239"/>
+      <c r="M3" s="239"/>
+      <c r="N3" s="232"/>
+      <c r="O3" s="239"/>
+      <c r="P3" s="240"/>
+      <c r="Q3" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R3" s="240"/>
+      <c r="S3" s="241"/>
+    </row>
+    <row r="4" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="225" t="s">
+        <v>685</v>
+      </c>
+      <c r="B4" s="236" t="s">
+        <v>686</v>
+      </c>
+      <c r="C4" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D4" s="228" t="s">
         <v>674</v>
       </c>
-      <c r="D3" s="233" t="s">
+      <c r="E4" s="228" t="s">
+        <v>675</v>
+      </c>
+      <c r="F4" s="228" t="s">
+        <v>687</v>
+      </c>
+      <c r="G4" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="228" t="s">
+        <v>688</v>
+      </c>
+      <c r="I4" s="239"/>
+      <c r="J4" s="239"/>
+      <c r="K4" s="239"/>
+      <c r="L4" s="239"/>
+      <c r="M4" s="239"/>
+      <c r="N4" s="232"/>
+      <c r="O4" s="239"/>
+      <c r="P4" s="240"/>
+      <c r="Q4" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R4" s="240"/>
+      <c r="S4" s="241"/>
+    </row>
+    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="242" t="s">
+        <v>689</v>
+      </c>
+      <c r="B5" s="243" t="s">
+        <v>681</v>
+      </c>
+      <c r="C5" s="244" t="s">
+        <v>673</v>
+      </c>
+      <c r="D5" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E5" s="228" t="s">
         <v>683</v>
       </c>
-      <c r="E3" s="233" t="s">
+      <c r="F5" s="228" t="s">
         <v>684</v>
       </c>
-      <c r="F3" s="233" t="s">
-        <v>685</v>
-      </c>
-      <c r="G3" s="243" t="n">
+      <c r="G5" s="238" t="n">
         <v>0.5</v>
       </c>
-      <c r="H3" s="233" t="s">
+      <c r="H5" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I5" s="239"/>
+      <c r="J5" s="239"/>
+      <c r="K5" s="239"/>
+      <c r="L5" s="239"/>
+      <c r="M5" s="239"/>
+      <c r="N5" s="232"/>
+      <c r="O5" s="239"/>
+      <c r="P5" s="240"/>
+      <c r="Q5" s="232" t="s">
         <v>679</v>
       </c>
-      <c r="I3" s="244"/>
-      <c r="J3" s="244"/>
-      <c r="K3" s="244"/>
-      <c r="L3" s="244"/>
-      <c r="M3" s="244"/>
-      <c r="N3" s="237"/>
-      <c r="O3" s="244"/>
-      <c r="P3" s="245"/>
-      <c r="Q3" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R3" s="245"/>
-      <c r="S3" s="246"/>
-    </row>
-    <row r="4" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="230" t="s">
+      <c r="R5" s="240"/>
+      <c r="S5" s="241"/>
+    </row>
+    <row r="6" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="235" t="s">
+        <v>690</v>
+      </c>
+      <c r="B6" s="229" t="s">
+        <v>681</v>
+      </c>
+      <c r="C6" s="245" t="s">
+        <v>673</v>
+      </c>
+      <c r="D6" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E6" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F6" s="228" t="s">
+        <v>684</v>
+      </c>
+      <c r="G6" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I6" s="239"/>
+      <c r="J6" s="239"/>
+      <c r="K6" s="239"/>
+      <c r="L6" s="239"/>
+      <c r="M6" s="239"/>
+      <c r="N6" s="232"/>
+      <c r="O6" s="246"/>
+      <c r="P6" s="247"/>
+      <c r="Q6" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R6" s="247"/>
+      <c r="S6" s="241"/>
+    </row>
+    <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="248" t="s">
+        <v>691</v>
+      </c>
+      <c r="B7" s="249" t="s">
         <v>686</v>
       </c>
-      <c r="B4" s="241" t="s">
+      <c r="C7" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D7" s="228" t="s">
+        <v>674</v>
+      </c>
+      <c r="E7" s="228" t="s">
+        <v>675</v>
+      </c>
+      <c r="F7" s="228" t="s">
         <v>687</v>
       </c>
-      <c r="C4" s="242" t="s">
+      <c r="G7" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="228" t="s">
+        <v>688</v>
+      </c>
+      <c r="I7" s="247"/>
+      <c r="J7" s="246"/>
+      <c r="K7" s="246"/>
+      <c r="L7" s="246"/>
+      <c r="M7" s="246"/>
+      <c r="N7" s="232"/>
+      <c r="O7" s="246"/>
+      <c r="P7" s="247"/>
+      <c r="Q7" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R7" s="247"/>
+      <c r="S7" s="20"/>
+    </row>
+    <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="250" t="s">
+        <v>692</v>
+      </c>
+      <c r="B8" s="226" t="s">
+        <v>681</v>
+      </c>
+      <c r="C8" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D8" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E8" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F8" s="228" t="s">
+        <v>684</v>
+      </c>
+      <c r="G8" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I8" s="247"/>
+      <c r="J8" s="246"/>
+      <c r="K8" s="246"/>
+      <c r="L8" s="246"/>
+      <c r="M8" s="246"/>
+      <c r="N8" s="232"/>
+      <c r="O8" s="239"/>
+      <c r="P8" s="240"/>
+      <c r="Q8" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R8" s="240"/>
+      <c r="S8" s="20"/>
+    </row>
+    <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="251" t="s">
+        <v>693</v>
+      </c>
+      <c r="B9" s="252" t="s">
+        <v>694</v>
+      </c>
+      <c r="C9" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D9" s="228" t="s">
         <v>674</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="E9" s="228" t="s">
         <v>675</v>
       </c>
-      <c r="E4" s="233" t="s">
+      <c r="F9" s="228" t="s">
+        <v>684</v>
+      </c>
+      <c r="G9" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I9" s="247"/>
+      <c r="J9" s="246"/>
+      <c r="K9" s="246"/>
+      <c r="L9" s="246"/>
+      <c r="M9" s="246"/>
+      <c r="N9" s="232"/>
+      <c r="O9" s="246"/>
+      <c r="P9" s="247"/>
+      <c r="Q9" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R9" s="253" t="s">
+        <v>695</v>
+      </c>
+      <c r="S9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="251" t="s">
+        <v>696</v>
+      </c>
+      <c r="B10" s="254" t="s">
+        <v>697</v>
+      </c>
+      <c r="C10" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D10" s="228" t="s">
+        <v>674</v>
+      </c>
+      <c r="E10" s="228" t="s">
+        <v>675</v>
+      </c>
+      <c r="F10" s="228" t="s">
+        <v>698</v>
+      </c>
+      <c r="G10" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H10" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I10" s="247"/>
+      <c r="J10" s="246"/>
+      <c r="K10" s="246"/>
+      <c r="L10" s="246"/>
+      <c r="M10" s="246"/>
+      <c r="N10" s="232"/>
+      <c r="O10" s="246"/>
+      <c r="P10" s="247"/>
+      <c r="Q10" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R10" s="253" t="s">
+        <v>695</v>
+      </c>
+      <c r="S10" s="20"/>
+    </row>
+    <row r="11" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="251" t="s">
+        <v>699</v>
+      </c>
+      <c r="B11" s="255" t="s">
+        <v>694</v>
+      </c>
+      <c r="C11" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D11" s="228" t="s">
+        <v>674</v>
+      </c>
+      <c r="E11" s="228" t="s">
+        <v>675</v>
+      </c>
+      <c r="F11" s="228" t="s">
+        <v>684</v>
+      </c>
+      <c r="G11" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H11" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I11" s="247"/>
+      <c r="J11" s="246"/>
+      <c r="K11" s="246"/>
+      <c r="L11" s="246"/>
+      <c r="M11" s="246"/>
+      <c r="N11" s="232"/>
+      <c r="O11" s="246"/>
+      <c r="P11" s="247"/>
+      <c r="Q11" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R11" s="253" t="s">
+        <v>695</v>
+      </c>
+      <c r="S11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="251" t="s">
+        <v>700</v>
+      </c>
+      <c r="B12" s="252" t="s">
+        <v>694</v>
+      </c>
+      <c r="C12" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D12" s="228" t="s">
+        <v>674</v>
+      </c>
+      <c r="E12" s="228" t="s">
+        <v>675</v>
+      </c>
+      <c r="F12" s="228" t="s">
+        <v>684</v>
+      </c>
+      <c r="G12" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I12" s="247"/>
+      <c r="J12" s="246"/>
+      <c r="K12" s="246"/>
+      <c r="L12" s="246"/>
+      <c r="M12" s="246"/>
+      <c r="N12" s="232"/>
+      <c r="O12" s="246"/>
+      <c r="P12" s="247"/>
+      <c r="Q12" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R12" s="253" t="s">
+        <v>695</v>
+      </c>
+      <c r="S12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="251" t="s">
+        <v>701</v>
+      </c>
+      <c r="B13" s="226" t="s">
+        <v>702</v>
+      </c>
+      <c r="C13" s="244" t="s">
+        <v>673</v>
+      </c>
+      <c r="D13" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E13" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F13" s="228" t="s">
+        <v>703</v>
+      </c>
+      <c r="G13" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I13" s="247"/>
+      <c r="J13" s="246"/>
+      <c r="K13" s="246"/>
+      <c r="L13" s="246"/>
+      <c r="M13" s="246"/>
+      <c r="N13" s="232"/>
+      <c r="O13" s="246"/>
+      <c r="P13" s="247"/>
+      <c r="Q13" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R13" s="247"/>
+      <c r="S13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="251" t="s">
+        <v>704</v>
+      </c>
+      <c r="B14" s="256" t="s">
+        <v>705</v>
+      </c>
+      <c r="C14" s="245" t="s">
+        <v>673</v>
+      </c>
+      <c r="D14" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E14" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F14" s="228" t="s">
+        <v>706</v>
+      </c>
+      <c r="G14" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="228" t="s">
+        <v>688</v>
+      </c>
+      <c r="I14" s="247"/>
+      <c r="J14" s="246"/>
+      <c r="K14" s="246"/>
+      <c r="L14" s="246"/>
+      <c r="M14" s="246"/>
+      <c r="N14" s="232"/>
+      <c r="O14" s="246"/>
+      <c r="P14" s="247"/>
+      <c r="Q14" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R14" s="247"/>
+      <c r="S14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="251" t="s">
+        <v>707</v>
+      </c>
+      <c r="B15" s="243" t="s">
+        <v>708</v>
+      </c>
+      <c r="C15" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D15" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E15" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F15" s="228" t="s">
+        <v>709</v>
+      </c>
+      <c r="G15" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I15" s="247"/>
+      <c r="J15" s="246"/>
+      <c r="K15" s="246"/>
+      <c r="L15" s="246"/>
+      <c r="M15" s="246"/>
+      <c r="N15" s="232"/>
+      <c r="O15" s="246"/>
+      <c r="P15" s="247"/>
+      <c r="Q15" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R15" s="247"/>
+      <c r="S15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="251" t="s">
+        <v>710</v>
+      </c>
+      <c r="B16" s="249" t="s">
+        <v>711</v>
+      </c>
+      <c r="C16" s="244" t="s">
+        <v>673</v>
+      </c>
+      <c r="D16" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E16" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F16" s="228" t="s">
+        <v>712</v>
+      </c>
+      <c r="G16" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H16" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I16" s="247"/>
+      <c r="J16" s="246"/>
+      <c r="K16" s="246"/>
+      <c r="L16" s="246"/>
+      <c r="M16" s="246"/>
+      <c r="N16" s="232"/>
+      <c r="O16" s="246"/>
+      <c r="P16" s="247"/>
+      <c r="Q16" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R16" s="247"/>
+      <c r="S16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="251" t="s">
+        <v>713</v>
+      </c>
+      <c r="B17" s="249" t="s">
+        <v>705</v>
+      </c>
+      <c r="C17" s="227" t="s">
+        <v>673</v>
+      </c>
+      <c r="D17" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E17" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F17" s="228" t="s">
+        <v>706</v>
+      </c>
+      <c r="G17" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H17" s="228" t="s">
+        <v>688</v>
+      </c>
+      <c r="I17" s="247"/>
+      <c r="J17" s="246"/>
+      <c r="K17" s="246"/>
+      <c r="L17" s="246"/>
+      <c r="M17" s="246"/>
+      <c r="N17" s="232"/>
+      <c r="O17" s="246"/>
+      <c r="P17" s="247"/>
+      <c r="Q17" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R17" s="247"/>
+      <c r="S17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="251" t="s">
+        <v>714</v>
+      </c>
+      <c r="B18" s="226" t="s">
+        <v>711</v>
+      </c>
+      <c r="C18" s="244" t="s">
+        <v>673</v>
+      </c>
+      <c r="D18" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E18" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F18" s="228" t="s">
+        <v>712</v>
+      </c>
+      <c r="G18" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H18" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I18" s="247"/>
+      <c r="J18" s="246"/>
+      <c r="K18" s="246"/>
+      <c r="L18" s="246"/>
+      <c r="M18" s="246"/>
+      <c r="N18" s="232"/>
+      <c r="O18" s="246"/>
+      <c r="P18" s="247"/>
+      <c r="Q18" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R18" s="247"/>
+      <c r="S18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="251" t="s">
+        <v>715</v>
+      </c>
+      <c r="B19" s="236" t="s">
+        <v>716</v>
+      </c>
+      <c r="C19" s="227" t="s">
+        <v>673</v>
+      </c>
+      <c r="D19" s="228" t="s">
+        <v>674</v>
+      </c>
+      <c r="E19" s="228" t="s">
+        <v>675</v>
+      </c>
+      <c r="F19" s="228" t="s">
+        <v>717</v>
+      </c>
+      <c r="G19" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H19" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I19" s="247"/>
+      <c r="J19" s="246"/>
+      <c r="K19" s="246"/>
+      <c r="L19" s="246"/>
+      <c r="M19" s="246"/>
+      <c r="N19" s="232"/>
+      <c r="O19" s="246"/>
+      <c r="P19" s="247"/>
+      <c r="Q19" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R19" s="247"/>
+      <c r="S19" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="251" t="s">
+        <v>718</v>
+      </c>
+      <c r="B20" s="243" t="s">
+        <v>719</v>
+      </c>
+      <c r="C20" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D20" s="228" t="s">
+        <v>720</v>
+      </c>
+      <c r="E20" s="228" t="s">
+        <v>675</v>
+      </c>
+      <c r="F20" s="228" t="s">
+        <v>721</v>
+      </c>
+      <c r="G20" s="228" t="s">
+        <v>722</v>
+      </c>
+      <c r="H20" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I20" s="247"/>
+      <c r="J20" s="246"/>
+      <c r="K20" s="246"/>
+      <c r="L20" s="246"/>
+      <c r="M20" s="246"/>
+      <c r="N20" s="232"/>
+      <c r="O20" s="246"/>
+      <c r="P20" s="247"/>
+      <c r="Q20" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R20" s="247"/>
+      <c r="S20" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="251" t="s">
+        <v>723</v>
+      </c>
+      <c r="B21" s="226" t="s">
+        <v>724</v>
+      </c>
+      <c r="C21" s="244" t="s">
+        <v>673</v>
+      </c>
+      <c r="D21" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E21" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F21" s="228" t="s">
+        <v>725</v>
+      </c>
+      <c r="G21" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H21" s="228" t="s">
+        <v>726</v>
+      </c>
+      <c r="I21" s="247"/>
+      <c r="J21" s="246"/>
+      <c r="K21" s="246"/>
+      <c r="L21" s="246"/>
+      <c r="M21" s="246"/>
+      <c r="N21" s="232"/>
+      <c r="O21" s="246"/>
+      <c r="P21" s="247"/>
+      <c r="Q21" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R21" s="247"/>
+      <c r="S21" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="251" t="s">
+        <v>727</v>
+      </c>
+      <c r="B22" s="236" t="s">
+        <v>681</v>
+      </c>
+      <c r="C22" s="227" t="s">
+        <v>673</v>
+      </c>
+      <c r="D22" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E22" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F22" s="228" t="s">
+        <v>684</v>
+      </c>
+      <c r="G22" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H22" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I22" s="247"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="246"/>
+      <c r="L22" s="246"/>
+      <c r="M22" s="246"/>
+      <c r="N22" s="232"/>
+      <c r="O22" s="246"/>
+      <c r="P22" s="247"/>
+      <c r="Q22" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R22" s="247"/>
+      <c r="S22" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="257" t="s">
+        <v>728</v>
+      </c>
+      <c r="B23" s="243" t="s">
+        <v>681</v>
+      </c>
+      <c r="C23" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D23" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E23" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F23" s="228" t="s">
+        <v>684</v>
+      </c>
+      <c r="G23" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H23" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I23" s="247"/>
+      <c r="J23" s="246"/>
+      <c r="K23" s="246"/>
+      <c r="L23" s="246"/>
+      <c r="M23" s="246"/>
+      <c r="N23" s="232"/>
+      <c r="O23" s="246"/>
+      <c r="P23" s="247"/>
+      <c r="Q23" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R23" s="247"/>
+      <c r="S23" s="20"/>
+    </row>
+    <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="258" t="s">
+        <v>729</v>
+      </c>
+      <c r="B24" s="226" t="s">
+        <v>730</v>
+      </c>
+      <c r="C24" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D24" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E24" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F24" s="228" t="s">
+        <v>731</v>
+      </c>
+      <c r="G24" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="228" t="s">
+        <v>688</v>
+      </c>
+      <c r="I24" s="247"/>
+      <c r="J24" s="246"/>
+      <c r="K24" s="259" t="s">
+        <v>642</v>
+      </c>
+      <c r="L24" s="259"/>
+      <c r="M24" s="259"/>
+      <c r="N24" s="232"/>
+      <c r="O24" s="246"/>
+      <c r="P24" s="247"/>
+      <c r="Q24" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R24" s="247"/>
+      <c r="S24" s="20"/>
+    </row>
+    <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="257" t="s">
+        <v>732</v>
+      </c>
+      <c r="B25" s="243" t="s">
+        <v>681</v>
+      </c>
+      <c r="C25" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D25" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E25" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F25" s="228" t="s">
+        <v>684</v>
+      </c>
+      <c r="G25" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I25" s="247"/>
+      <c r="J25" s="246"/>
+      <c r="K25" s="246"/>
+      <c r="L25" s="246"/>
+      <c r="M25" s="246"/>
+      <c r="N25" s="232"/>
+      <c r="O25" s="246"/>
+      <c r="P25" s="247"/>
+      <c r="Q25" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R25" s="247"/>
+      <c r="S25" s="20"/>
+    </row>
+    <row r="26" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="248" t="s">
+        <v>733</v>
+      </c>
+      <c r="B26" s="226" t="s">
+        <v>734</v>
+      </c>
+      <c r="C26" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D26" s="228" t="s">
+        <v>720</v>
+      </c>
+      <c r="E26" s="228" t="s">
+        <v>675</v>
+      </c>
+      <c r="F26" s="228" t="s">
+        <v>735</v>
+      </c>
+      <c r="G26" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H26" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I26" s="247"/>
+      <c r="J26" s="246"/>
+      <c r="K26" s="260" t="s">
+        <v>647</v>
+      </c>
+      <c r="L26" s="260" t="s">
+        <v>650</v>
+      </c>
+      <c r="M26" s="260" t="s">
+        <v>651</v>
+      </c>
+      <c r="N26" s="232"/>
+      <c r="O26" s="246"/>
+      <c r="P26" s="247"/>
+      <c r="Q26" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R26" s="247"/>
+      <c r="S26" s="20"/>
+    </row>
+    <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="251" t="s">
+        <v>736</v>
+      </c>
+      <c r="B27" s="236" t="s">
+        <v>737</v>
+      </c>
+      <c r="C27" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D27" s="228" t="s">
+        <v>674</v>
+      </c>
+      <c r="E27" s="228" t="s">
+        <v>738</v>
+      </c>
+      <c r="F27" s="228" t="s">
+        <v>684</v>
+      </c>
+      <c r="G27" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H27" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I27" s="247"/>
+      <c r="J27" s="246"/>
+      <c r="K27" s="246"/>
+      <c r="L27" s="246"/>
+      <c r="M27" s="246"/>
+      <c r="N27" s="232"/>
+      <c r="O27" s="246"/>
+      <c r="P27" s="247"/>
+      <c r="Q27" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R27" s="247"/>
+      <c r="S27" s="20"/>
+    </row>
+    <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="257" t="s">
+        <v>739</v>
+      </c>
+      <c r="B28" s="261" t="s">
+        <v>740</v>
+      </c>
+      <c r="C28" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D28" s="228" t="s">
+        <v>674</v>
+      </c>
+      <c r="E28" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F28" s="228" t="s">
+        <v>684</v>
+      </c>
+      <c r="G28" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H28" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I28" s="247"/>
+      <c r="J28" s="246"/>
+      <c r="K28" s="246"/>
+      <c r="L28" s="246"/>
+      <c r="M28" s="246"/>
+      <c r="N28" s="232"/>
+      <c r="O28" s="246"/>
+      <c r="P28" s="247"/>
+      <c r="Q28" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R28" s="253" t="s">
+        <v>695</v>
+      </c>
+      <c r="S28" s="20"/>
+    </row>
+    <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="262" t="s">
+        <v>741</v>
+      </c>
+      <c r="B29" s="261" t="s">
+        <v>742</v>
+      </c>
+      <c r="C29" s="244" t="s">
+        <v>673</v>
+      </c>
+      <c r="D29" s="228" t="s">
+        <v>674</v>
+      </c>
+      <c r="E29" s="228" t="s">
+        <v>743</v>
+      </c>
+      <c r="F29" s="228" t="s">
+        <v>744</v>
+      </c>
+      <c r="G29" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H29" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I29" s="247"/>
+      <c r="J29" s="246"/>
+      <c r="K29" s="246"/>
+      <c r="L29" s="246"/>
+      <c r="M29" s="246"/>
+      <c r="N29" s="232"/>
+      <c r="O29" s="246"/>
+      <c r="P29" s="247"/>
+      <c r="Q29" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R29" s="253" t="s">
+        <v>695</v>
+      </c>
+      <c r="S29" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="262" t="s">
+        <v>745</v>
+      </c>
+      <c r="B30" s="236" t="s">
+        <v>746</v>
+      </c>
+      <c r="C30" s="227" t="s">
+        <v>673</v>
+      </c>
+      <c r="D30" s="228" t="s">
+        <v>747</v>
+      </c>
+      <c r="E30" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F30" s="228" t="s">
+        <v>744</v>
+      </c>
+      <c r="G30" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H30" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I30" s="247"/>
+      <c r="J30" s="246"/>
+      <c r="K30" s="246"/>
+      <c r="L30" s="246"/>
+      <c r="M30" s="246"/>
+      <c r="N30" s="232"/>
+      <c r="O30" s="246"/>
+      <c r="P30" s="247"/>
+      <c r="Q30" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R30" s="247"/>
+      <c r="S30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="262" t="s">
+        <v>748</v>
+      </c>
+      <c r="B31" s="236" t="s">
+        <v>749</v>
+      </c>
+      <c r="C31" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D31" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E31" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F31" s="228" t="s">
+        <v>750</v>
+      </c>
+      <c r="G31" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H31" s="228" t="s">
+        <v>688</v>
+      </c>
+      <c r="I31" s="247"/>
+      <c r="J31" s="246"/>
+      <c r="K31" s="246"/>
+      <c r="L31" s="246"/>
+      <c r="M31" s="246"/>
+      <c r="N31" s="232"/>
+      <c r="O31" s="246"/>
+      <c r="P31" s="247"/>
+      <c r="Q31" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R31" s="247"/>
+      <c r="S31" s="20"/>
+    </row>
+    <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="262" t="s">
+        <v>751</v>
+      </c>
+      <c r="B32" s="243" t="s">
+        <v>752</v>
+      </c>
+      <c r="C32" s="244" t="s">
+        <v>673</v>
+      </c>
+      <c r="D32" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E32" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F32" s="228" t="s">
+        <v>698</v>
+      </c>
+      <c r="G32" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H32" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I32" s="247"/>
+      <c r="J32" s="246"/>
+      <c r="K32" s="246"/>
+      <c r="L32" s="246"/>
+      <c r="M32" s="246"/>
+      <c r="N32" s="232"/>
+      <c r="O32" s="246"/>
+      <c r="P32" s="247"/>
+      <c r="Q32" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R32" s="247"/>
+      <c r="S32" s="20"/>
+    </row>
+    <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="262" t="s">
+        <v>753</v>
+      </c>
+      <c r="B33" s="226" t="s">
+        <v>681</v>
+      </c>
+      <c r="C33" s="227" t="s">
+        <v>673</v>
+      </c>
+      <c r="D33" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E33" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F33" s="228" t="s">
+        <v>684</v>
+      </c>
+      <c r="G33" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H33" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I33" s="247"/>
+      <c r="J33" s="246"/>
+      <c r="K33" s="246"/>
+      <c r="L33" s="246"/>
+      <c r="M33" s="246"/>
+      <c r="N33" s="232"/>
+      <c r="O33" s="246"/>
+      <c r="P33" s="247"/>
+      <c r="Q33" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R33" s="247"/>
+      <c r="S33" s="20"/>
+    </row>
+    <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="262" t="s">
+        <v>754</v>
+      </c>
+      <c r="B34" s="236" t="s">
+        <v>755</v>
+      </c>
+      <c r="C34" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D34" s="228" t="s">
+        <v>682</v>
+      </c>
+      <c r="E34" s="228" t="s">
+        <v>683</v>
+      </c>
+      <c r="F34" s="228" t="s">
+        <v>756</v>
+      </c>
+      <c r="G34" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H34" s="228" t="s">
+        <v>726</v>
+      </c>
+      <c r="I34" s="247"/>
+      <c r="J34" s="246"/>
+      <c r="K34" s="246"/>
+      <c r="L34" s="246"/>
+      <c r="M34" s="246"/>
+      <c r="N34" s="232"/>
+      <c r="O34" s="246"/>
+      <c r="P34" s="247"/>
+      <c r="Q34" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R34" s="247"/>
+      <c r="S34" s="20"/>
+    </row>
+    <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="258" t="s">
+        <v>757</v>
+      </c>
+      <c r="B35" s="236" t="s">
+        <v>758</v>
+      </c>
+      <c r="C35" s="244" t="s">
+        <v>673</v>
+      </c>
+      <c r="D35" s="228" t="s">
+        <v>674</v>
+      </c>
+      <c r="E35" s="228" t="s">
+        <v>675</v>
+      </c>
+      <c r="F35" s="228" t="s">
         <v>676</v>
       </c>
-      <c r="F4" s="233" t="s">
-        <v>688</v>
-      </c>
-      <c r="G4" s="243" t="n">
+      <c r="G35" s="238" t="n">
         <v>0.5</v>
       </c>
-      <c r="H4" s="233" t="s">
-        <v>689</v>
-      </c>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="M4" s="244"/>
-      <c r="N4" s="237"/>
-      <c r="O4" s="244"/>
-      <c r="P4" s="245"/>
-      <c r="Q4" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R4" s="245"/>
-      <c r="S4" s="246"/>
-    </row>
-    <row r="5" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="247" t="s">
-        <v>690</v>
-      </c>
-      <c r="B5" s="248" t="s">
-        <v>682</v>
-      </c>
-      <c r="C5" s="249" t="s">
+      <c r="H35" s="228" t="s">
+        <v>678</v>
+      </c>
+      <c r="I35" s="247"/>
+      <c r="J35" s="246"/>
+      <c r="K35" s="246"/>
+      <c r="L35" s="246"/>
+      <c r="M35" s="246"/>
+      <c r="N35" s="232"/>
+      <c r="O35" s="246"/>
+      <c r="P35" s="247"/>
+      <c r="Q35" s="232" t="s">
+        <v>679</v>
+      </c>
+      <c r="R35" s="247"/>
+      <c r="S35" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="257" t="s">
+        <v>759</v>
+      </c>
+      <c r="B36" s="236" t="s">
+        <v>760</v>
+      </c>
+      <c r="C36" s="227" t="s">
+        <v>673</v>
+      </c>
+      <c r="D36" s="228" t="s">
         <v>674</v>
       </c>
-      <c r="D5" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E5" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F5" s="233" t="s">
-        <v>685</v>
-      </c>
-      <c r="G5" s="243" t="n">
+      <c r="E36" s="228" t="s">
+        <v>675</v>
+      </c>
+      <c r="F36" s="246" t="s">
+        <v>761</v>
+      </c>
+      <c r="G36" s="238" t="n">
         <v>0.5</v>
       </c>
-      <c r="H5" s="233" t="s">
+      <c r="H36" s="228" t="s">
+        <v>762</v>
+      </c>
+      <c r="I36" s="247"/>
+      <c r="J36" s="246"/>
+      <c r="K36" s="246"/>
+      <c r="L36" s="246"/>
+      <c r="M36" s="246"/>
+      <c r="N36" s="232"/>
+      <c r="O36" s="246"/>
+      <c r="P36" s="247"/>
+      <c r="Q36" s="232"/>
+      <c r="R36" s="247"/>
+      <c r="S36" s="20"/>
+    </row>
+    <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="263" t="s">
+        <v>763</v>
+      </c>
+      <c r="B37" s="243" t="s">
+        <v>764</v>
+      </c>
+      <c r="C37" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D37" s="228" t="s">
+        <v>674</v>
+      </c>
+      <c r="E37" s="228" t="s">
+        <v>675</v>
+      </c>
+      <c r="F37" s="228" t="s">
+        <v>765</v>
+      </c>
+      <c r="G37" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H37" s="228" t="s">
+        <v>766</v>
+      </c>
+      <c r="I37" s="264"/>
+      <c r="J37" s="264"/>
+      <c r="K37" s="246"/>
+      <c r="L37" s="246"/>
+      <c r="M37" s="246"/>
+      <c r="N37" s="232"/>
+      <c r="O37" s="264"/>
+      <c r="P37" s="253"/>
+      <c r="Q37" s="253"/>
+      <c r="R37" s="253"/>
+      <c r="S37" s="265"/>
+    </row>
+    <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="266" t="s">
+        <v>767</v>
+      </c>
+      <c r="B38" s="226" t="s">
+        <v>768</v>
+      </c>
+      <c r="C38" s="237" t="s">
+        <v>673</v>
+      </c>
+      <c r="D38" s="228" t="s">
+        <v>674</v>
+      </c>
+      <c r="E38" s="228" t="s">
+        <v>675</v>
+      </c>
+      <c r="F38" s="228" t="s">
+        <v>765</v>
+      </c>
+      <c r="G38" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H38" s="228" t="s">
+        <v>769</v>
+      </c>
+      <c r="I38" s="264"/>
+      <c r="J38" s="264"/>
+      <c r="K38" s="246"/>
+      <c r="L38" s="246"/>
+      <c r="M38" s="246"/>
+      <c r="N38" s="232"/>
+      <c r="O38" s="264"/>
+      <c r="P38" s="253"/>
+      <c r="Q38" s="253"/>
+      <c r="R38" s="253"/>
+      <c r="S38" s="265"/>
+    </row>
+    <row r="39" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="267" t="s">
+        <v>770</v>
+      </c>
+      <c r="B39" s="243" t="s">
+        <v>760</v>
+      </c>
+      <c r="C39" s="244"/>
+      <c r="D39" s="228"/>
+      <c r="E39" s="228"/>
+      <c r="F39" s="228"/>
+      <c r="G39" s="238"/>
+      <c r="H39" s="228"/>
+      <c r="I39" s="264"/>
+      <c r="J39" s="264"/>
+      <c r="K39" s="246"/>
+      <c r="L39" s="246"/>
+      <c r="M39" s="246"/>
+      <c r="N39" s="232"/>
+      <c r="O39" s="264"/>
+      <c r="P39" s="253"/>
+      <c r="Q39" s="253"/>
+      <c r="R39" s="253"/>
+      <c r="S39" s="265"/>
+    </row>
+    <row r="40" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="263" t="s">
+        <v>771</v>
+      </c>
+      <c r="B40" s="226" t="s">
+        <v>772</v>
+      </c>
+      <c r="C40" s="268" t="s">
+        <v>673</v>
+      </c>
+      <c r="D40" s="228" t="s">
+        <v>674</v>
+      </c>
+      <c r="E40" s="228" t="s">
+        <v>675</v>
+      </c>
+      <c r="F40" s="228" t="s">
+        <v>773</v>
+      </c>
+      <c r="G40" s="238" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H40" s="228" t="s">
+        <v>774</v>
+      </c>
+      <c r="I40" s="264"/>
+      <c r="J40" s="264"/>
+      <c r="K40" s="246"/>
+      <c r="L40" s="246"/>
+      <c r="M40" s="246"/>
+      <c r="N40" s="232"/>
+      <c r="O40" s="264"/>
+      <c r="P40" s="253"/>
+      <c r="Q40" s="253" t="s">
         <v>679</v>
       </c>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
-      <c r="M5" s="244"/>
-      <c r="N5" s="237"/>
-      <c r="O5" s="244"/>
-      <c r="P5" s="245"/>
-      <c r="Q5" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R5" s="245"/>
-      <c r="S5" s="246"/>
-    </row>
-    <row r="6" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="240" t="s">
-        <v>691</v>
-      </c>
-      <c r="B6" s="234" t="s">
-        <v>682</v>
-      </c>
-      <c r="C6" s="250" t="s">
+      <c r="R40" s="253"/>
+      <c r="S40" s="265"/>
+    </row>
+    <row r="41" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="263" t="s">
+        <v>775</v>
+      </c>
+      <c r="B41" s="243" t="s">
+        <v>776</v>
+      </c>
+      <c r="C41" s="227" t="s">
+        <v>673</v>
+      </c>
+      <c r="D41" s="228" t="s">
         <v>674</v>
       </c>
-      <c r="D6" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E6" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F6" s="233" t="s">
-        <v>685</v>
-      </c>
-      <c r="G6" s="243" t="n">
+      <c r="E41" s="228" t="s">
+        <v>675</v>
+      </c>
+      <c r="F41" s="228" t="s">
+        <v>773</v>
+      </c>
+      <c r="G41" s="238" t="n">
         <v>0.5</v>
       </c>
-      <c r="H6" s="233" t="s">
+      <c r="H41" s="228" t="s">
+        <v>769</v>
+      </c>
+      <c r="I41" s="264"/>
+      <c r="J41" s="264"/>
+      <c r="K41" s="246"/>
+      <c r="L41" s="246"/>
+      <c r="M41" s="246"/>
+      <c r="N41" s="232"/>
+      <c r="O41" s="264"/>
+      <c r="P41" s="253"/>
+      <c r="Q41" s="253" t="s">
         <v>679</v>
       </c>
-      <c r="I6" s="244"/>
-      <c r="J6" s="244"/>
-      <c r="K6" s="244"/>
-      <c r="L6" s="244"/>
-      <c r="M6" s="244"/>
-      <c r="N6" s="237"/>
-      <c r="O6" s="251"/>
-      <c r="P6" s="252"/>
-      <c r="Q6" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R6" s="252"/>
-      <c r="S6" s="246"/>
-    </row>
-    <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="253" t="s">
-        <v>692</v>
-      </c>
-      <c r="B7" s="254" t="s">
-        <v>687</v>
-      </c>
-      <c r="C7" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D7" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E7" s="233" t="s">
-        <v>676</v>
-      </c>
-      <c r="F7" s="233" t="s">
-        <v>688</v>
-      </c>
-      <c r="G7" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H7" s="233" t="s">
-        <v>689</v>
-      </c>
-      <c r="I7" s="252"/>
-      <c r="J7" s="251"/>
-      <c r="K7" s="251"/>
-      <c r="L7" s="251"/>
-      <c r="M7" s="251"/>
-      <c r="N7" s="237"/>
-      <c r="O7" s="251"/>
-      <c r="P7" s="252"/>
-      <c r="Q7" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R7" s="252"/>
-      <c r="S7" s="20"/>
-    </row>
-    <row r="8" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="255" t="s">
-        <v>693</v>
-      </c>
-      <c r="B8" s="231" t="s">
-        <v>682</v>
-      </c>
-      <c r="C8" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D8" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E8" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F8" s="233" t="s">
-        <v>685</v>
-      </c>
-      <c r="G8" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H8" s="233" t="s">
+      <c r="R41" s="253"/>
+      <c r="S41" s="265"/>
+    </row>
+    <row r="42" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="263" t="s">
+        <v>777</v>
+      </c>
+      <c r="B42" s="226" t="s">
+        <v>778</v>
+      </c>
+      <c r="C42" s="269" t="s">
+        <v>779</v>
+      </c>
+      <c r="D42" s="270"/>
+      <c r="E42" s="228" t="s">
+        <v>780</v>
+      </c>
+      <c r="F42" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G42" s="264"/>
+      <c r="H42" s="228" t="s">
+        <v>782</v>
+      </c>
+      <c r="I42" s="228" t="s">
+        <v>783</v>
+      </c>
+      <c r="J42" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K42" s="246"/>
+      <c r="L42" s="246"/>
+      <c r="M42" s="246"/>
+      <c r="N42" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O42" s="253" t="s">
+        <v>786</v>
+      </c>
+      <c r="P42" s="253" t="n">
+        <v>100168</v>
+      </c>
+      <c r="Q42" s="253" t="s">
         <v>679</v>
       </c>
-      <c r="I8" s="252"/>
-      <c r="J8" s="251"/>
-      <c r="K8" s="251"/>
-      <c r="L8" s="251"/>
-      <c r="M8" s="251"/>
-      <c r="N8" s="237"/>
-      <c r="O8" s="244"/>
-      <c r="P8" s="245"/>
-      <c r="Q8" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R8" s="245"/>
-      <c r="S8" s="20"/>
-    </row>
-    <row r="9" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="256" t="s">
-        <v>694</v>
-      </c>
-      <c r="B9" s="257" t="s">
-        <v>695</v>
-      </c>
-      <c r="C9" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D9" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E9" s="233" t="s">
-        <v>676</v>
-      </c>
-      <c r="F9" s="233" t="s">
-        <v>685</v>
-      </c>
-      <c r="G9" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H9" s="233" t="s">
+      <c r="R42" s="253"/>
+      <c r="S42" s="265"/>
+    </row>
+    <row r="43" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="263" t="s">
+        <v>787</v>
+      </c>
+      <c r="B43" s="243" t="s">
+        <v>778</v>
+      </c>
+      <c r="C43" s="271" t="s">
+        <v>779</v>
+      </c>
+      <c r="D43" s="264"/>
+      <c r="E43" s="228" t="s">
+        <v>780</v>
+      </c>
+      <c r="F43" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G43" s="264"/>
+      <c r="H43" s="228" t="s">
+        <v>782</v>
+      </c>
+      <c r="I43" s="228" t="s">
+        <v>783</v>
+      </c>
+      <c r="J43" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K43" s="246"/>
+      <c r="L43" s="246"/>
+      <c r="M43" s="246"/>
+      <c r="N43" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O43" s="253" t="s">
+        <v>786</v>
+      </c>
+      <c r="P43" s="253" t="n">
+        <v>100166</v>
+      </c>
+      <c r="Q43" s="253" t="s">
         <v>679</v>
       </c>
-      <c r="I9" s="252"/>
-      <c r="J9" s="251"/>
-      <c r="K9" s="251"/>
-      <c r="L9" s="251"/>
-      <c r="M9" s="251"/>
-      <c r="N9" s="237"/>
-      <c r="O9" s="251"/>
-      <c r="P9" s="252"/>
-      <c r="Q9" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R9" s="258" t="s">
-        <v>696</v>
-      </c>
-      <c r="S9" s="20"/>
-    </row>
-    <row r="10" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="256" t="s">
-        <v>697</v>
-      </c>
-      <c r="B10" s="259" t="s">
-        <v>698</v>
-      </c>
-      <c r="C10" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D10" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E10" s="233" t="s">
-        <v>676</v>
-      </c>
-      <c r="F10" s="233" t="s">
-        <v>699</v>
-      </c>
-      <c r="G10" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H10" s="233" t="s">
+      <c r="R43" s="253"/>
+      <c r="S43" s="265"/>
+    </row>
+    <row r="44" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="266" t="s">
+        <v>788</v>
+      </c>
+      <c r="B44" s="249" t="s">
+        <v>778</v>
+      </c>
+      <c r="C44" s="272" t="s">
+        <v>779</v>
+      </c>
+      <c r="D44" s="264"/>
+      <c r="E44" s="228" t="s">
+        <v>780</v>
+      </c>
+      <c r="F44" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G44" s="264"/>
+      <c r="H44" s="228" t="s">
+        <v>782</v>
+      </c>
+      <c r="I44" s="228" t="s">
+        <v>783</v>
+      </c>
+      <c r="J44" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K44" s="246"/>
+      <c r="L44" s="246"/>
+      <c r="M44" s="246"/>
+      <c r="N44" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O44" s="253" t="s">
+        <v>786</v>
+      </c>
+      <c r="P44" s="253" t="n">
+        <v>100167</v>
+      </c>
+      <c r="Q44" s="253" t="s">
         <v>679</v>
       </c>
-      <c r="I10" s="252"/>
-      <c r="J10" s="251"/>
-      <c r="K10" s="251"/>
-      <c r="L10" s="251"/>
-      <c r="M10" s="251"/>
-      <c r="N10" s="237"/>
-      <c r="O10" s="251"/>
-      <c r="P10" s="252"/>
-      <c r="Q10" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R10" s="258" t="s">
-        <v>696</v>
-      </c>
-      <c r="S10" s="20"/>
-    </row>
-    <row r="11" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="256" t="s">
-        <v>700</v>
-      </c>
-      <c r="B11" s="260" t="s">
-        <v>695</v>
-      </c>
-      <c r="C11" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D11" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E11" s="233" t="s">
-        <v>676</v>
-      </c>
-      <c r="F11" s="233" t="s">
-        <v>685</v>
-      </c>
-      <c r="G11" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H11" s="233" t="s">
+      <c r="R44" s="253"/>
+      <c r="S44" s="265"/>
+    </row>
+    <row r="45" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="273" t="s">
+        <v>789</v>
+      </c>
+      <c r="B45" s="249" t="s">
+        <v>790</v>
+      </c>
+      <c r="C45" s="272" t="s">
+        <v>779</v>
+      </c>
+      <c r="D45" s="264"/>
+      <c r="E45" s="228" t="s">
+        <v>780</v>
+      </c>
+      <c r="F45" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G45" s="264"/>
+      <c r="H45" s="228" t="s">
+        <v>782</v>
+      </c>
+      <c r="I45" s="228" t="s">
+        <v>783</v>
+      </c>
+      <c r="J45" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K45" s="246"/>
+      <c r="L45" s="246"/>
+      <c r="M45" s="246"/>
+      <c r="N45" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O45" s="253" t="s">
+        <v>786</v>
+      </c>
+      <c r="P45" s="253" t="n">
+        <v>100169</v>
+      </c>
+      <c r="Q45" s="253" t="s">
+        <v>791</v>
+      </c>
+      <c r="R45" s="253"/>
+      <c r="S45" s="265"/>
+    </row>
+    <row r="46" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="253" t="s">
+        <v>792</v>
+      </c>
+      <c r="B46" s="274" t="s">
+        <v>790</v>
+      </c>
+      <c r="C46" s="269" t="s">
+        <v>779</v>
+      </c>
+      <c r="D46" s="264"/>
+      <c r="E46" s="228" t="s">
+        <v>780</v>
+      </c>
+      <c r="F46" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G46" s="264"/>
+      <c r="H46" s="228" t="s">
+        <v>782</v>
+      </c>
+      <c r="I46" s="228" t="s">
+        <v>783</v>
+      </c>
+      <c r="J46" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K46" s="246"/>
+      <c r="L46" s="246"/>
+      <c r="M46" s="246"/>
+      <c r="N46" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O46" s="253" t="s">
+        <v>786</v>
+      </c>
+      <c r="P46" s="253" t="n">
+        <v>100170</v>
+      </c>
+      <c r="Q46" s="253" t="s">
+        <v>791</v>
+      </c>
+      <c r="R46" s="253"/>
+      <c r="S46" s="265"/>
+    </row>
+    <row r="47" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="266" t="s">
+        <v>793</v>
+      </c>
+      <c r="B47" s="243" t="s">
+        <v>794</v>
+      </c>
+      <c r="C47" s="271" t="s">
+        <v>779</v>
+      </c>
+      <c r="D47" s="264"/>
+      <c r="E47" s="228" t="s">
+        <v>780</v>
+      </c>
+      <c r="F47" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G47" s="264"/>
+      <c r="H47" s="228" t="s">
+        <v>782</v>
+      </c>
+      <c r="I47" s="228" t="s">
+        <v>783</v>
+      </c>
+      <c r="J47" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K47" s="246"/>
+      <c r="L47" s="246"/>
+      <c r="M47" s="246"/>
+      <c r="N47" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O47" s="253" t="s">
+        <v>795</v>
+      </c>
+      <c r="P47" s="253" t="n">
+        <v>100165</v>
+      </c>
+      <c r="Q47" s="253" t="s">
+        <v>791</v>
+      </c>
+      <c r="R47" s="253"/>
+      <c r="S47" s="265"/>
+    </row>
+    <row r="48" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="253" t="s">
+        <v>796</v>
+      </c>
+      <c r="B48" s="274" t="s">
+        <v>794</v>
+      </c>
+      <c r="C48" s="272" t="s">
+        <v>779</v>
+      </c>
+      <c r="D48" s="264"/>
+      <c r="E48" s="228" t="s">
+        <v>780</v>
+      </c>
+      <c r="F48" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G48" s="264"/>
+      <c r="H48" s="228" t="s">
+        <v>782</v>
+      </c>
+      <c r="I48" s="228" t="s">
+        <v>783</v>
+      </c>
+      <c r="J48" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K48" s="246"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O48" s="253" t="s">
+        <v>795</v>
+      </c>
+      <c r="P48" s="253" t="n">
+        <v>100164</v>
+      </c>
+      <c r="Q48" s="253" t="s">
+        <v>791</v>
+      </c>
+      <c r="R48" s="253"/>
+      <c r="S48" s="265"/>
+    </row>
+    <row r="49" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="266" t="s">
+        <v>797</v>
+      </c>
+      <c r="B49" s="243" t="s">
+        <v>798</v>
+      </c>
+      <c r="C49" s="267" t="s">
+        <v>799</v>
+      </c>
+      <c r="D49" s="264"/>
+      <c r="E49" s="228" t="s">
+        <v>800</v>
+      </c>
+      <c r="F49" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G49" s="264"/>
+      <c r="H49" s="228" t="s">
+        <v>801</v>
+      </c>
+      <c r="I49" s="228"/>
+      <c r="J49" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K49" s="246"/>
+      <c r="L49" s="246"/>
+      <c r="M49" s="246"/>
+      <c r="N49" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O49" s="253" t="s">
+        <v>802</v>
+      </c>
+      <c r="P49" s="253" t="s">
+        <v>803</v>
+      </c>
+      <c r="Q49" s="253" t="s">
         <v>679</v>
       </c>
-      <c r="I11" s="252"/>
-      <c r="J11" s="251"/>
-      <c r="K11" s="251"/>
-      <c r="L11" s="251"/>
-      <c r="M11" s="251"/>
-      <c r="N11" s="237"/>
-      <c r="O11" s="251"/>
-      <c r="P11" s="252"/>
-      <c r="Q11" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R11" s="258" t="s">
-        <v>696</v>
-      </c>
-      <c r="S11" s="20"/>
-    </row>
-    <row r="12" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="256" t="s">
-        <v>701</v>
-      </c>
-      <c r="B12" s="257" t="s">
-        <v>695</v>
-      </c>
-      <c r="C12" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D12" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E12" s="233" t="s">
-        <v>676</v>
-      </c>
-      <c r="F12" s="233" t="s">
-        <v>685</v>
-      </c>
-      <c r="G12" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H12" s="233" t="s">
+      <c r="R49" s="253"/>
+      <c r="S49" s="265"/>
+    </row>
+    <row r="50" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="275" t="s">
+        <v>804</v>
+      </c>
+      <c r="B50" s="276" t="s">
+        <v>805</v>
+      </c>
+      <c r="C50" s="266" t="s">
+        <v>799</v>
+      </c>
+      <c r="D50" s="264"/>
+      <c r="E50" s="228" t="s">
+        <v>800</v>
+      </c>
+      <c r="F50" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G50" s="264"/>
+      <c r="H50" s="228" t="s">
+        <v>806</v>
+      </c>
+      <c r="I50" s="228" t="s">
+        <v>807</v>
+      </c>
+      <c r="J50" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K50" s="246"/>
+      <c r="L50" s="246"/>
+      <c r="M50" s="246"/>
+      <c r="N50" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O50" s="253" t="s">
+        <v>808</v>
+      </c>
+      <c r="P50" s="253" t="s">
+        <v>809</v>
+      </c>
+      <c r="Q50" s="253" t="s">
         <v>679</v>
       </c>
-      <c r="I12" s="252"/>
-      <c r="J12" s="251"/>
-      <c r="K12" s="251"/>
-      <c r="L12" s="251"/>
-      <c r="M12" s="251"/>
-      <c r="N12" s="237"/>
-      <c r="O12" s="251"/>
-      <c r="P12" s="252"/>
-      <c r="Q12" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R12" s="258" t="s">
-        <v>696</v>
-      </c>
-      <c r="S12" s="20"/>
-    </row>
-    <row r="13" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="256" t="s">
-        <v>702</v>
-      </c>
-      <c r="B13" s="231" t="s">
-        <v>703</v>
-      </c>
-      <c r="C13" s="249" t="s">
-        <v>674</v>
-      </c>
-      <c r="D13" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E13" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F13" s="233" t="s">
-        <v>704</v>
-      </c>
-      <c r="G13" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H13" s="233" t="s">
+      <c r="R50" s="253"/>
+      <c r="S50" s="265"/>
+    </row>
+    <row r="51" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="253" t="s">
+        <v>810</v>
+      </c>
+      <c r="B51" s="274" t="s">
+        <v>811</v>
+      </c>
+      <c r="C51" s="267" t="s">
+        <v>799</v>
+      </c>
+      <c r="D51" s="264"/>
+      <c r="E51" s="228" t="s">
+        <v>812</v>
+      </c>
+      <c r="F51" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G51" s="264"/>
+      <c r="H51" s="228" t="s">
+        <v>813</v>
+      </c>
+      <c r="I51" s="228"/>
+      <c r="J51" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K51" s="246"/>
+      <c r="L51" s="246"/>
+      <c r="M51" s="246"/>
+      <c r="N51" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O51" s="253" t="s">
+        <v>814</v>
+      </c>
+      <c r="P51" s="253" t="n">
+        <v>100162</v>
+      </c>
+      <c r="Q51" s="253" t="s">
         <v>679</v>
       </c>
-      <c r="I13" s="252"/>
-      <c r="J13" s="251"/>
-      <c r="K13" s="251"/>
-      <c r="L13" s="251"/>
-      <c r="M13" s="251"/>
-      <c r="N13" s="237"/>
-      <c r="O13" s="251"/>
-      <c r="P13" s="252"/>
-      <c r="Q13" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R13" s="252"/>
-      <c r="S13" s="20"/>
-    </row>
-    <row r="14" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="256" t="s">
-        <v>705</v>
-      </c>
-      <c r="B14" s="261" t="s">
-        <v>706</v>
-      </c>
-      <c r="C14" s="250" t="s">
-        <v>674</v>
-      </c>
-      <c r="D14" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E14" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F14" s="233" t="s">
-        <v>707</v>
-      </c>
-      <c r="G14" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H14" s="233" t="s">
-        <v>689</v>
-      </c>
-      <c r="I14" s="252"/>
-      <c r="J14" s="251"/>
-      <c r="K14" s="251"/>
-      <c r="L14" s="251"/>
-      <c r="M14" s="251"/>
-      <c r="N14" s="237"/>
-      <c r="O14" s="251"/>
-      <c r="P14" s="252"/>
-      <c r="Q14" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R14" s="252"/>
-      <c r="S14" s="20"/>
-    </row>
-    <row r="15" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="256" t="s">
-        <v>708</v>
-      </c>
-      <c r="B15" s="248" t="s">
-        <v>709</v>
-      </c>
-      <c r="C15" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D15" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E15" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F15" s="233" t="s">
-        <v>710</v>
-      </c>
-      <c r="G15" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H15" s="233" t="s">
+      <c r="R51" s="253"/>
+      <c r="S51" s="265"/>
+    </row>
+    <row r="52" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="266" t="s">
+        <v>815</v>
+      </c>
+      <c r="B52" s="236" t="s">
+        <v>816</v>
+      </c>
+      <c r="C52" s="266" t="s">
+        <v>799</v>
+      </c>
+      <c r="D52" s="264"/>
+      <c r="E52" s="228" t="s">
+        <v>812</v>
+      </c>
+      <c r="F52" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G52" s="264"/>
+      <c r="H52" s="228" t="s">
+        <v>813</v>
+      </c>
+      <c r="I52" s="228" t="s">
+        <v>783</v>
+      </c>
+      <c r="J52" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K52" s="246"/>
+      <c r="L52" s="246"/>
+      <c r="M52" s="246"/>
+      <c r="N52" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O52" s="253" t="s">
+        <v>814</v>
+      </c>
+      <c r="P52" s="253" t="n">
+        <v>100163</v>
+      </c>
+      <c r="Q52" s="253" t="s">
         <v>679</v>
       </c>
-      <c r="I15" s="252"/>
-      <c r="J15" s="251"/>
-      <c r="K15" s="251"/>
-      <c r="L15" s="251"/>
-      <c r="M15" s="251"/>
-      <c r="N15" s="237"/>
-      <c r="O15" s="251"/>
-      <c r="P15" s="252"/>
-      <c r="Q15" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R15" s="252"/>
-      <c r="S15" s="20"/>
-    </row>
-    <row r="16" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="256" t="s">
-        <v>711</v>
-      </c>
-      <c r="B16" s="254" t="s">
-        <v>712</v>
-      </c>
-      <c r="C16" s="249" t="s">
-        <v>674</v>
-      </c>
-      <c r="D16" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E16" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F16" s="233" t="s">
-        <v>713</v>
-      </c>
-      <c r="G16" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H16" s="233" t="s">
+      <c r="R52" s="253"/>
+      <c r="S52" s="265"/>
+    </row>
+    <row r="53" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="273" t="s">
+        <v>817</v>
+      </c>
+      <c r="B53" s="243" t="s">
+        <v>818</v>
+      </c>
+      <c r="C53" s="273" t="s">
+        <v>799</v>
+      </c>
+      <c r="D53" s="264"/>
+      <c r="E53" s="228" t="s">
+        <v>800</v>
+      </c>
+      <c r="F53" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G53" s="264"/>
+      <c r="H53" s="228" t="s">
+        <v>806</v>
+      </c>
+      <c r="I53" s="228"/>
+      <c r="J53" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K53" s="246"/>
+      <c r="L53" s="246"/>
+      <c r="M53" s="246"/>
+      <c r="N53" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O53" s="253" t="s">
+        <v>808</v>
+      </c>
+      <c r="P53" s="253" t="s">
+        <v>819</v>
+      </c>
+      <c r="Q53" s="253" t="s">
+        <v>791</v>
+      </c>
+      <c r="R53" s="253"/>
+      <c r="S53" s="265"/>
+    </row>
+    <row r="54" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="273" t="s">
+        <v>820</v>
+      </c>
+      <c r="B54" s="249" t="s">
+        <v>821</v>
+      </c>
+      <c r="C54" s="267" t="s">
+        <v>799</v>
+      </c>
+      <c r="D54" s="264"/>
+      <c r="E54" s="228" t="s">
+        <v>800</v>
+      </c>
+      <c r="F54" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G54" s="264"/>
+      <c r="H54" s="228" t="s">
+        <v>806</v>
+      </c>
+      <c r="I54" s="228" t="s">
+        <v>783</v>
+      </c>
+      <c r="J54" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K54" s="246"/>
+      <c r="L54" s="246"/>
+      <c r="M54" s="246"/>
+      <c r="N54" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>808</v>
+      </c>
+      <c r="P54" s="253" t="s">
+        <v>822</v>
+      </c>
+      <c r="Q54" s="253" t="s">
+        <v>791</v>
+      </c>
+      <c r="R54" s="253"/>
+      <c r="S54" s="265"/>
+    </row>
+    <row r="55" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="273" t="s">
+        <v>823</v>
+      </c>
+      <c r="B55" s="249" t="s">
+        <v>824</v>
+      </c>
+      <c r="C55" s="266" t="s">
+        <v>799</v>
+      </c>
+      <c r="D55" s="264"/>
+      <c r="E55" s="228" t="s">
+        <v>812</v>
+      </c>
+      <c r="F55" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G55" s="264"/>
+      <c r="H55" s="228" t="s">
+        <v>825</v>
+      </c>
+      <c r="I55" s="228" t="s">
+        <v>826</v>
+      </c>
+      <c r="J55" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K55" s="246"/>
+      <c r="L55" s="246"/>
+      <c r="M55" s="246"/>
+      <c r="N55" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>827</v>
+      </c>
+      <c r="P55" s="253" t="n">
+        <v>170166</v>
+      </c>
+      <c r="Q55" s="253" t="s">
         <v>679</v>
       </c>
-      <c r="I16" s="252"/>
-      <c r="J16" s="251"/>
-      <c r="K16" s="251"/>
-      <c r="L16" s="251"/>
-      <c r="M16" s="251"/>
-      <c r="N16" s="237"/>
-      <c r="O16" s="251"/>
-      <c r="P16" s="252"/>
-      <c r="Q16" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R16" s="252"/>
-      <c r="S16" s="20"/>
-    </row>
-    <row r="17" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="256" t="s">
-        <v>714</v>
-      </c>
-      <c r="B17" s="254" t="s">
-        <v>706</v>
-      </c>
-      <c r="C17" s="232" t="s">
-        <v>674</v>
-      </c>
-      <c r="D17" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E17" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F17" s="233" t="s">
-        <v>707</v>
-      </c>
-      <c r="G17" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H17" s="233" t="s">
-        <v>689</v>
-      </c>
-      <c r="I17" s="252"/>
-      <c r="J17" s="251"/>
-      <c r="K17" s="251"/>
-      <c r="L17" s="251"/>
-      <c r="M17" s="251"/>
-      <c r="N17" s="237"/>
-      <c r="O17" s="251"/>
-      <c r="P17" s="252"/>
-      <c r="Q17" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R17" s="252"/>
-      <c r="S17" s="20"/>
-    </row>
-    <row r="18" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="256" t="s">
-        <v>715</v>
-      </c>
-      <c r="B18" s="231" t="s">
-        <v>712</v>
-      </c>
-      <c r="C18" s="249" t="s">
-        <v>674</v>
-      </c>
-      <c r="D18" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E18" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F18" s="233" t="s">
-        <v>713</v>
-      </c>
-      <c r="G18" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H18" s="233" t="s">
+      <c r="R55" s="253"/>
+      <c r="S55" s="265"/>
+    </row>
+    <row r="56" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="275" t="s">
+        <v>828</v>
+      </c>
+      <c r="B56" s="274" t="s">
+        <v>824</v>
+      </c>
+      <c r="C56" s="273" t="s">
+        <v>799</v>
+      </c>
+      <c r="D56" s="264"/>
+      <c r="E56" s="228" t="s">
+        <v>812</v>
+      </c>
+      <c r="F56" s="228" t="s">
+        <v>781</v>
+      </c>
+      <c r="G56" s="264"/>
+      <c r="H56" s="228" t="s">
+        <v>825</v>
+      </c>
+      <c r="I56" s="228" t="s">
+        <v>826</v>
+      </c>
+      <c r="J56" s="228" t="s">
+        <v>784</v>
+      </c>
+      <c r="K56" s="246"/>
+      <c r="L56" s="246"/>
+      <c r="M56" s="246"/>
+      <c r="N56" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O56" s="253" t="s">
+        <v>827</v>
+      </c>
+      <c r="P56" s="253" t="n">
+        <v>170165</v>
+      </c>
+      <c r="Q56" s="253" t="s">
         <v>679</v>
       </c>
-      <c r="I18" s="252"/>
-      <c r="J18" s="251"/>
-      <c r="K18" s="251"/>
-      <c r="L18" s="251"/>
-      <c r="M18" s="251"/>
-      <c r="N18" s="237"/>
-      <c r="O18" s="251"/>
-      <c r="P18" s="252"/>
-      <c r="Q18" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R18" s="252"/>
-      <c r="S18" s="20"/>
-    </row>
-    <row r="19" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="256" t="s">
-        <v>716</v>
-      </c>
-      <c r="B19" s="241" t="s">
-        <v>717</v>
-      </c>
-      <c r="C19" s="232" t="s">
-        <v>674</v>
-      </c>
-      <c r="D19" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E19" s="233" t="s">
-        <v>676</v>
-      </c>
-      <c r="F19" s="233" t="s">
-        <v>718</v>
-      </c>
-      <c r="G19" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H19" s="233" t="s">
+      <c r="R56" s="253"/>
+      <c r="S56" s="265"/>
+    </row>
+    <row r="57" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="273" t="s">
+        <v>829</v>
+      </c>
+      <c r="B57" s="243" t="s">
+        <v>830</v>
+      </c>
+      <c r="C57" s="273" t="s">
+        <v>779</v>
+      </c>
+      <c r="D57" s="264"/>
+      <c r="E57" s="228" t="s">
+        <v>831</v>
+      </c>
+      <c r="F57" s="228" t="s">
+        <v>832</v>
+      </c>
+      <c r="G57" s="228" t="s">
+        <v>833</v>
+      </c>
+      <c r="H57" s="228" t="s">
+        <v>834</v>
+      </c>
+      <c r="I57" s="228" t="s">
+        <v>835</v>
+      </c>
+      <c r="J57" s="228"/>
+      <c r="K57" s="264"/>
+      <c r="L57" s="264"/>
+      <c r="M57" s="264"/>
+      <c r="N57" s="232" t="s">
+        <v>785</v>
+      </c>
+      <c r="O57" s="253"/>
+      <c r="P57" s="253" t="n">
+        <v>200505</v>
+      </c>
+      <c r="Q57" s="253" t="s">
         <v>679</v>
       </c>
-      <c r="I19" s="252"/>
-      <c r="J19" s="251"/>
-      <c r="K19" s="251"/>
-      <c r="L19" s="251"/>
-      <c r="M19" s="251"/>
-      <c r="N19" s="237"/>
-      <c r="O19" s="251"/>
-      <c r="P19" s="252"/>
-      <c r="Q19" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R19" s="252"/>
-      <c r="S19" s="20"/>
-    </row>
-    <row r="20" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="256" t="s">
-        <v>719</v>
-      </c>
-      <c r="B20" s="248" t="s">
-        <v>720</v>
-      </c>
-      <c r="C20" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D20" s="233" t="s">
-        <v>721</v>
-      </c>
-      <c r="E20" s="233" t="s">
-        <v>676</v>
-      </c>
-      <c r="F20" s="233" t="s">
-        <v>722</v>
-      </c>
-      <c r="G20" s="233" t="s">
-        <v>723</v>
-      </c>
-      <c r="H20" s="233" t="s">
+      <c r="R57" s="253"/>
+      <c r="S57" s="265"/>
+    </row>
+    <row r="58" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="267" t="s">
+        <v>836</v>
+      </c>
+      <c r="B58" s="249" t="s">
+        <v>837</v>
+      </c>
+      <c r="C58" s="269" t="s">
+        <v>779</v>
+      </c>
+      <c r="D58" s="264"/>
+      <c r="E58" s="228" t="s">
+        <v>838</v>
+      </c>
+      <c r="F58" s="228" t="s">
+        <v>839</v>
+      </c>
+      <c r="G58" s="228" t="s">
+        <v>840</v>
+      </c>
+      <c r="H58" s="228" t="s">
+        <v>841</v>
+      </c>
+      <c r="I58" s="228" t="s">
+        <v>842</v>
+      </c>
+      <c r="J58" s="228"/>
+      <c r="K58" s="264"/>
+      <c r="L58" s="264"/>
+      <c r="M58" s="264"/>
+      <c r="N58" s="232" t="s">
+        <v>843</v>
+      </c>
+      <c r="O58" s="253" t="s">
+        <v>844</v>
+      </c>
+      <c r="P58" s="253"/>
+      <c r="Q58" s="253" t="s">
         <v>679</v>
       </c>
-      <c r="I20" s="252"/>
-      <c r="J20" s="251"/>
-      <c r="K20" s="251"/>
-      <c r="L20" s="251"/>
-      <c r="M20" s="251"/>
-      <c r="N20" s="237"/>
-      <c r="O20" s="251"/>
-      <c r="P20" s="252"/>
-      <c r="Q20" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R20" s="252"/>
-      <c r="S20" s="20"/>
-    </row>
-    <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="256" t="s">
-        <v>724</v>
-      </c>
-      <c r="B21" s="231" t="s">
-        <v>725</v>
-      </c>
-      <c r="C21" s="249" t="s">
-        <v>674</v>
-      </c>
-      <c r="D21" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E21" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F21" s="233" t="s">
-        <v>726</v>
-      </c>
-      <c r="G21" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H21" s="233" t="s">
-        <v>727</v>
-      </c>
-      <c r="I21" s="252"/>
-      <c r="J21" s="251"/>
-      <c r="K21" s="251"/>
-      <c r="L21" s="251"/>
-      <c r="M21" s="251"/>
-      <c r="N21" s="237"/>
-      <c r="O21" s="251"/>
-      <c r="P21" s="252"/>
-      <c r="Q21" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R21" s="252"/>
-      <c r="S21" s="20"/>
-    </row>
-    <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="256" t="s">
-        <v>728</v>
-      </c>
-      <c r="B22" s="241" t="s">
-        <v>682</v>
-      </c>
-      <c r="C22" s="232" t="s">
-        <v>674</v>
-      </c>
-      <c r="D22" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E22" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F22" s="233" t="s">
-        <v>685</v>
-      </c>
-      <c r="G22" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H22" s="233" t="s">
-        <v>679</v>
-      </c>
-      <c r="I22" s="252"/>
-      <c r="J22" s="251"/>
-      <c r="K22" s="251"/>
-      <c r="L22" s="251"/>
-      <c r="M22" s="251"/>
-      <c r="N22" s="237"/>
-      <c r="O22" s="251"/>
-      <c r="P22" s="252"/>
-      <c r="Q22" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R22" s="252"/>
-      <c r="S22" s="20"/>
-    </row>
-    <row r="23" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="262" t="s">
-        <v>729</v>
-      </c>
-      <c r="B23" s="248" t="s">
-        <v>682</v>
-      </c>
-      <c r="C23" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D23" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E23" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F23" s="233" t="s">
-        <v>685</v>
-      </c>
-      <c r="G23" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H23" s="233" t="s">
-        <v>679</v>
-      </c>
-      <c r="I23" s="252"/>
-      <c r="J23" s="251"/>
-      <c r="K23" s="251"/>
-      <c r="L23" s="251"/>
-      <c r="M23" s="251"/>
-      <c r="N23" s="237"/>
-      <c r="O23" s="251"/>
-      <c r="P23" s="252"/>
-      <c r="Q23" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R23" s="252"/>
-      <c r="S23" s="20"/>
-    </row>
-    <row r="24" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="263" t="s">
-        <v>730</v>
-      </c>
-      <c r="B24" s="231" t="s">
-        <v>731</v>
-      </c>
-      <c r="C24" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D24" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E24" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F24" s="233" t="s">
-        <v>732</v>
-      </c>
-      <c r="G24" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H24" s="233" t="s">
-        <v>689</v>
-      </c>
-      <c r="I24" s="252"/>
-      <c r="J24" s="251"/>
-      <c r="K24" s="264" t="s">
-        <v>643</v>
-      </c>
-      <c r="L24" s="264"/>
-      <c r="M24" s="264"/>
-      <c r="N24" s="237"/>
-      <c r="O24" s="251"/>
-      <c r="P24" s="252"/>
-      <c r="Q24" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R24" s="252"/>
-      <c r="S24" s="20"/>
-    </row>
-    <row r="25" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="262" t="s">
-        <v>733</v>
-      </c>
-      <c r="B25" s="248" t="s">
-        <v>682</v>
-      </c>
-      <c r="C25" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D25" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E25" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F25" s="233" t="s">
-        <v>685</v>
-      </c>
-      <c r="G25" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H25" s="233" t="s">
-        <v>679</v>
-      </c>
-      <c r="I25" s="252"/>
-      <c r="J25" s="251"/>
-      <c r="K25" s="251"/>
-      <c r="L25" s="251"/>
-      <c r="M25" s="251"/>
-      <c r="N25" s="237"/>
-      <c r="O25" s="251"/>
-      <c r="P25" s="252"/>
-      <c r="Q25" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R25" s="252"/>
-      <c r="S25" s="20"/>
-    </row>
-    <row r="26" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="253" t="s">
-        <v>734</v>
-      </c>
-      <c r="B26" s="231" t="s">
-        <v>735</v>
-      </c>
-      <c r="C26" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D26" s="233" t="s">
-        <v>721</v>
-      </c>
-      <c r="E26" s="233" t="s">
-        <v>676</v>
-      </c>
-      <c r="F26" s="233" t="s">
-        <v>736</v>
-      </c>
-      <c r="G26" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H26" s="233" t="s">
-        <v>679</v>
-      </c>
-      <c r="I26" s="252"/>
-      <c r="J26" s="251"/>
-      <c r="K26" s="265" t="s">
-        <v>648</v>
-      </c>
-      <c r="L26" s="265" t="s">
-        <v>651</v>
-      </c>
-      <c r="M26" s="265" t="s">
-        <v>652</v>
-      </c>
-      <c r="N26" s="237"/>
-      <c r="O26" s="251"/>
-      <c r="P26" s="252"/>
-      <c r="Q26" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R26" s="252"/>
-      <c r="S26" s="20"/>
-    </row>
-    <row r="27" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="256" t="s">
-        <v>737</v>
-      </c>
-      <c r="B27" s="241" t="s">
-        <v>738</v>
-      </c>
-      <c r="C27" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D27" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E27" s="233" t="s">
-        <v>739</v>
-      </c>
-      <c r="F27" s="233" t="s">
-        <v>685</v>
-      </c>
-      <c r="G27" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H27" s="233" t="s">
-        <v>679</v>
-      </c>
-      <c r="I27" s="252"/>
-      <c r="J27" s="251"/>
-      <c r="K27" s="251"/>
-      <c r="L27" s="251"/>
-      <c r="M27" s="251"/>
-      <c r="N27" s="237"/>
-      <c r="O27" s="251"/>
-      <c r="P27" s="252"/>
-      <c r="Q27" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R27" s="252"/>
-      <c r="S27" s="20"/>
-    </row>
-    <row r="28" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="262" t="s">
-        <v>740</v>
-      </c>
-      <c r="B28" s="266" t="s">
-        <v>741</v>
-      </c>
-      <c r="C28" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D28" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E28" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F28" s="233" t="s">
-        <v>685</v>
-      </c>
-      <c r="G28" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H28" s="233" t="s">
-        <v>679</v>
-      </c>
-      <c r="I28" s="252"/>
-      <c r="J28" s="251"/>
-      <c r="K28" s="251"/>
-      <c r="L28" s="251"/>
-      <c r="M28" s="251"/>
-      <c r="N28" s="237"/>
-      <c r="O28" s="251"/>
-      <c r="P28" s="252"/>
-      <c r="Q28" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R28" s="258" t="s">
-        <v>696</v>
-      </c>
-      <c r="S28" s="20"/>
-    </row>
-    <row r="29" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="267" t="s">
-        <v>742</v>
-      </c>
-      <c r="B29" s="266" t="s">
-        <v>743</v>
-      </c>
-      <c r="C29" s="249" t="s">
-        <v>674</v>
-      </c>
-      <c r="D29" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E29" s="233" t="s">
-        <v>744</v>
-      </c>
-      <c r="F29" s="233" t="s">
-        <v>745</v>
-      </c>
-      <c r="G29" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H29" s="233" t="s">
-        <v>679</v>
-      </c>
-      <c r="I29" s="252"/>
-      <c r="J29" s="251"/>
-      <c r="K29" s="251"/>
-      <c r="L29" s="251"/>
-      <c r="M29" s="251"/>
-      <c r="N29" s="237"/>
-      <c r="O29" s="251"/>
-      <c r="P29" s="252"/>
-      <c r="Q29" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R29" s="258" t="s">
-        <v>696</v>
-      </c>
-      <c r="S29" s="20"/>
-    </row>
-    <row r="30" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="267" t="s">
-        <v>746</v>
-      </c>
-      <c r="B30" s="241" t="s">
-        <v>747</v>
-      </c>
-      <c r="C30" s="232" t="s">
-        <v>674</v>
-      </c>
-      <c r="D30" s="233" t="s">
-        <v>748</v>
-      </c>
-      <c r="E30" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F30" s="233" t="s">
-        <v>745</v>
-      </c>
-      <c r="G30" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H30" s="233" t="s">
-        <v>679</v>
-      </c>
-      <c r="I30" s="252"/>
-      <c r="J30" s="251"/>
-      <c r="K30" s="251"/>
-      <c r="L30" s="251"/>
-      <c r="M30" s="251"/>
-      <c r="N30" s="237"/>
-      <c r="O30" s="251"/>
-      <c r="P30" s="252"/>
-      <c r="Q30" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R30" s="252"/>
-      <c r="S30" s="20"/>
-    </row>
-    <row r="31" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="267" t="s">
-        <v>749</v>
-      </c>
-      <c r="B31" s="241" t="s">
-        <v>750</v>
-      </c>
-      <c r="C31" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D31" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E31" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F31" s="233" t="s">
-        <v>751</v>
-      </c>
-      <c r="G31" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H31" s="233" t="s">
-        <v>689</v>
-      </c>
-      <c r="I31" s="252"/>
-      <c r="J31" s="251"/>
-      <c r="K31" s="251"/>
-      <c r="L31" s="251"/>
-      <c r="M31" s="251"/>
-      <c r="N31" s="237"/>
-      <c r="O31" s="251"/>
-      <c r="P31" s="252"/>
-      <c r="Q31" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R31" s="252"/>
-      <c r="S31" s="20"/>
-    </row>
-    <row r="32" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="267" t="s">
-        <v>752</v>
-      </c>
-      <c r="B32" s="248" t="s">
-        <v>753</v>
-      </c>
-      <c r="C32" s="249" t="s">
-        <v>674</v>
-      </c>
-      <c r="D32" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E32" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F32" s="233" t="s">
-        <v>699</v>
-      </c>
-      <c r="G32" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H32" s="233" t="s">
-        <v>679</v>
-      </c>
-      <c r="I32" s="252"/>
-      <c r="J32" s="251"/>
-      <c r="K32" s="251"/>
-      <c r="L32" s="251"/>
-      <c r="M32" s="251"/>
-      <c r="N32" s="237"/>
-      <c r="O32" s="251"/>
-      <c r="P32" s="252"/>
-      <c r="Q32" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R32" s="252"/>
-      <c r="S32" s="20"/>
-    </row>
-    <row r="33" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="267" t="s">
-        <v>754</v>
-      </c>
-      <c r="B33" s="231" t="s">
-        <v>682</v>
-      </c>
-      <c r="C33" s="232" t="s">
-        <v>674</v>
-      </c>
-      <c r="D33" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E33" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F33" s="233" t="s">
-        <v>685</v>
-      </c>
-      <c r="G33" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H33" s="233" t="s">
-        <v>679</v>
-      </c>
-      <c r="I33" s="252"/>
-      <c r="J33" s="251"/>
-      <c r="K33" s="251"/>
-      <c r="L33" s="251"/>
-      <c r="M33" s="251"/>
-      <c r="N33" s="237"/>
-      <c r="O33" s="251"/>
-      <c r="P33" s="252"/>
-      <c r="Q33" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R33" s="252"/>
-      <c r="S33" s="20"/>
-    </row>
-    <row r="34" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="267" t="s">
-        <v>755</v>
-      </c>
-      <c r="B34" s="241" t="s">
-        <v>756</v>
-      </c>
-      <c r="C34" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D34" s="233" t="s">
-        <v>683</v>
-      </c>
-      <c r="E34" s="233" t="s">
-        <v>684</v>
-      </c>
-      <c r="F34" s="233" t="s">
-        <v>757</v>
-      </c>
-      <c r="G34" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H34" s="233" t="s">
-        <v>727</v>
-      </c>
-      <c r="I34" s="252"/>
-      <c r="J34" s="251"/>
-      <c r="K34" s="251"/>
-      <c r="L34" s="251"/>
-      <c r="M34" s="251"/>
-      <c r="N34" s="237"/>
-      <c r="O34" s="251"/>
-      <c r="P34" s="252"/>
-      <c r="Q34" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R34" s="252"/>
-      <c r="S34" s="20"/>
-    </row>
-    <row r="35" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="263" t="s">
-        <v>758</v>
-      </c>
-      <c r="B35" s="241" t="s">
-        <v>759</v>
-      </c>
-      <c r="C35" s="249" t="s">
-        <v>674</v>
-      </c>
-      <c r="D35" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E35" s="233" t="s">
-        <v>676</v>
-      </c>
-      <c r="F35" s="233" t="s">
-        <v>677</v>
-      </c>
-      <c r="G35" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H35" s="233" t="s">
-        <v>679</v>
-      </c>
-      <c r="I35" s="252"/>
-      <c r="J35" s="251"/>
-      <c r="K35" s="251"/>
-      <c r="L35" s="251"/>
-      <c r="M35" s="251"/>
-      <c r="N35" s="237"/>
-      <c r="O35" s="251"/>
-      <c r="P35" s="252"/>
-      <c r="Q35" s="237" t="s">
-        <v>680</v>
-      </c>
-      <c r="R35" s="252"/>
-      <c r="S35" s="20"/>
-    </row>
-    <row r="36" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="262" t="s">
-        <v>760</v>
-      </c>
-      <c r="B36" s="241" t="s">
-        <v>761</v>
-      </c>
-      <c r="C36" s="232" t="s">
-        <v>674</v>
-      </c>
-      <c r="D36" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E36" s="233" t="s">
-        <v>676</v>
-      </c>
-      <c r="F36" s="251" t="s">
-        <v>762</v>
-      </c>
-      <c r="G36" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H36" s="233" t="s">
-        <v>763</v>
-      </c>
-      <c r="I36" s="252"/>
-      <c r="J36" s="251"/>
-      <c r="K36" s="251"/>
-      <c r="L36" s="251"/>
-      <c r="M36" s="251"/>
-      <c r="N36" s="237"/>
-      <c r="O36" s="251"/>
-      <c r="P36" s="252"/>
-      <c r="Q36" s="237"/>
-      <c r="R36" s="252"/>
-      <c r="S36" s="20"/>
-    </row>
-    <row r="37" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="268" t="s">
-        <v>764</v>
-      </c>
-      <c r="B37" s="248" t="s">
-        <v>765</v>
-      </c>
-      <c r="C37" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D37" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E37" s="233" t="s">
-        <v>676</v>
-      </c>
-      <c r="F37" s="233" t="s">
-        <v>766</v>
-      </c>
-      <c r="G37" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H37" s="233" t="s">
-        <v>767</v>
-      </c>
-      <c r="I37" s="269"/>
-      <c r="J37" s="269"/>
-      <c r="K37" s="251"/>
-      <c r="L37" s="251"/>
-      <c r="M37" s="251"/>
-      <c r="N37" s="237"/>
-      <c r="O37" s="269"/>
-      <c r="P37" s="258"/>
-      <c r="Q37" s="258"/>
-      <c r="R37" s="258"/>
-      <c r="S37" s="270"/>
-    </row>
-    <row r="38" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="271" t="s">
-        <v>768</v>
-      </c>
-      <c r="B38" s="231" t="s">
-        <v>769</v>
-      </c>
-      <c r="C38" s="242" t="s">
-        <v>674</v>
-      </c>
-      <c r="D38" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E38" s="233" t="s">
-        <v>676</v>
-      </c>
-      <c r="F38" s="233" t="s">
-        <v>766</v>
-      </c>
-      <c r="G38" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H38" s="233" t="s">
-        <v>770</v>
-      </c>
-      <c r="I38" s="269"/>
-      <c r="J38" s="269"/>
-      <c r="K38" s="251"/>
-      <c r="L38" s="251"/>
-      <c r="M38" s="251"/>
-      <c r="N38" s="237"/>
-      <c r="O38" s="269"/>
-      <c r="P38" s="258"/>
-      <c r="Q38" s="258"/>
-      <c r="R38" s="258"/>
-      <c r="S38" s="270"/>
-    </row>
-    <row r="39" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="272" t="s">
-        <v>771</v>
-      </c>
-      <c r="B39" s="248" t="s">
-        <v>761</v>
-      </c>
-      <c r="C39" s="249"/>
-      <c r="D39" s="233"/>
-      <c r="E39" s="233"/>
-      <c r="F39" s="233"/>
-      <c r="G39" s="243"/>
-      <c r="H39" s="233"/>
-      <c r="I39" s="269"/>
-      <c r="J39" s="269"/>
-      <c r="K39" s="251"/>
-      <c r="L39" s="251"/>
-      <c r="M39" s="251"/>
-      <c r="N39" s="237"/>
-      <c r="O39" s="269"/>
-      <c r="P39" s="258"/>
-      <c r="Q39" s="258"/>
-      <c r="R39" s="258"/>
-      <c r="S39" s="270"/>
-    </row>
-    <row r="40" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="268" t="s">
-        <v>772</v>
-      </c>
-      <c r="B40" s="231" t="s">
-        <v>773</v>
-      </c>
-      <c r="C40" s="273" t="s">
-        <v>674</v>
-      </c>
-      <c r="D40" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E40" s="233" t="s">
-        <v>676</v>
-      </c>
-      <c r="F40" s="233" t="s">
-        <v>774</v>
-      </c>
-      <c r="G40" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H40" s="233" t="s">
-        <v>775</v>
-      </c>
-      <c r="I40" s="269"/>
-      <c r="J40" s="269"/>
-      <c r="K40" s="251"/>
-      <c r="L40" s="251"/>
-      <c r="M40" s="251"/>
-      <c r="N40" s="237"/>
-      <c r="O40" s="269"/>
-      <c r="P40" s="258"/>
-      <c r="Q40" s="258" t="s">
-        <v>680</v>
-      </c>
-      <c r="R40" s="258"/>
-      <c r="S40" s="270"/>
-    </row>
-    <row r="41" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="268" t="s">
-        <v>776</v>
-      </c>
-      <c r="B41" s="248" t="s">
-        <v>777</v>
-      </c>
-      <c r="C41" s="232" t="s">
-        <v>674</v>
-      </c>
-      <c r="D41" s="233" t="s">
-        <v>675</v>
-      </c>
-      <c r="E41" s="233" t="s">
-        <v>676</v>
-      </c>
-      <c r="F41" s="233" t="s">
-        <v>774</v>
-      </c>
-      <c r="G41" s="243" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H41" s="233" t="s">
-        <v>770</v>
-      </c>
-      <c r="I41" s="269"/>
-      <c r="J41" s="269"/>
-      <c r="K41" s="251"/>
-      <c r="L41" s="251"/>
-      <c r="M41" s="251"/>
-      <c r="N41" s="237"/>
-      <c r="O41" s="269"/>
-      <c r="P41" s="258"/>
-      <c r="Q41" s="258" t="s">
-        <v>680</v>
-      </c>
-      <c r="R41" s="258"/>
-      <c r="S41" s="270"/>
-    </row>
-    <row r="42" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="268" t="s">
-        <v>778</v>
-      </c>
-      <c r="B42" s="231" t="s">
-        <v>779</v>
-      </c>
-      <c r="C42" s="274" t="s">
-        <v>780</v>
-      </c>
-      <c r="D42" s="275"/>
-      <c r="E42" s="233" t="s">
-        <v>781</v>
-      </c>
-      <c r="F42" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G42" s="269"/>
-      <c r="H42" s="233" t="s">
-        <v>783</v>
-      </c>
-      <c r="I42" s="233" t="s">
-        <v>784</v>
-      </c>
-      <c r="J42" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K42" s="251"/>
-      <c r="L42" s="251"/>
-      <c r="M42" s="251"/>
-      <c r="N42" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O42" s="258" t="s">
-        <v>787</v>
-      </c>
-      <c r="P42" s="258" t="n">
-        <v>100168</v>
-      </c>
-      <c r="Q42" s="258" t="s">
-        <v>680</v>
-      </c>
-      <c r="R42" s="258"/>
-      <c r="S42" s="270"/>
-    </row>
-    <row r="43" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="268" t="s">
-        <v>788</v>
-      </c>
-      <c r="B43" s="248" t="s">
-        <v>779</v>
-      </c>
-      <c r="C43" s="276" t="s">
-        <v>780</v>
-      </c>
-      <c r="D43" s="269"/>
-      <c r="E43" s="233" t="s">
-        <v>781</v>
-      </c>
-      <c r="F43" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G43" s="269"/>
-      <c r="H43" s="233" t="s">
-        <v>783</v>
-      </c>
-      <c r="I43" s="233" t="s">
-        <v>784</v>
-      </c>
-      <c r="J43" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K43" s="251"/>
-      <c r="L43" s="251"/>
-      <c r="M43" s="251"/>
-      <c r="N43" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O43" s="258" t="s">
-        <v>787</v>
-      </c>
-      <c r="P43" s="258" t="n">
-        <v>100166</v>
-      </c>
-      <c r="Q43" s="258" t="s">
-        <v>680</v>
-      </c>
-      <c r="R43" s="258"/>
-      <c r="S43" s="270"/>
-    </row>
-    <row r="44" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="271" t="s">
-        <v>789</v>
-      </c>
-      <c r="B44" s="254" t="s">
-        <v>779</v>
-      </c>
-      <c r="C44" s="277" t="s">
-        <v>780</v>
-      </c>
-      <c r="D44" s="269"/>
-      <c r="E44" s="233" t="s">
-        <v>781</v>
-      </c>
-      <c r="F44" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G44" s="269"/>
-      <c r="H44" s="233" t="s">
-        <v>783</v>
-      </c>
-      <c r="I44" s="233" t="s">
-        <v>784</v>
-      </c>
-      <c r="J44" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K44" s="251"/>
-      <c r="L44" s="251"/>
-      <c r="M44" s="251"/>
-      <c r="N44" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O44" s="258" t="s">
-        <v>787</v>
-      </c>
-      <c r="P44" s="258" t="n">
-        <v>100167</v>
-      </c>
-      <c r="Q44" s="258" t="s">
-        <v>680</v>
-      </c>
-      <c r="R44" s="258"/>
-      <c r="S44" s="270"/>
-    </row>
-    <row r="45" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="278" t="s">
-        <v>790</v>
-      </c>
-      <c r="B45" s="254" t="s">
-        <v>791</v>
-      </c>
-      <c r="C45" s="277" t="s">
-        <v>780</v>
-      </c>
-      <c r="D45" s="269"/>
-      <c r="E45" s="233" t="s">
-        <v>781</v>
-      </c>
-      <c r="F45" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G45" s="269"/>
-      <c r="H45" s="233" t="s">
-        <v>783</v>
-      </c>
-      <c r="I45" s="233" t="s">
-        <v>784</v>
-      </c>
-      <c r="J45" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K45" s="251"/>
-      <c r="L45" s="251"/>
-      <c r="M45" s="251"/>
-      <c r="N45" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O45" s="258" t="s">
-        <v>787</v>
-      </c>
-      <c r="P45" s="258" t="n">
-        <v>100169</v>
-      </c>
-      <c r="Q45" s="258" t="s">
-        <v>792</v>
-      </c>
-      <c r="R45" s="258"/>
-      <c r="S45" s="270"/>
-    </row>
-    <row r="46" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="258" t="s">
-        <v>793</v>
-      </c>
-      <c r="B46" s="279" t="s">
-        <v>791</v>
-      </c>
-      <c r="C46" s="274" t="s">
-        <v>780</v>
-      </c>
-      <c r="D46" s="269"/>
-      <c r="E46" s="233" t="s">
-        <v>781</v>
-      </c>
-      <c r="F46" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G46" s="269"/>
-      <c r="H46" s="233" t="s">
-        <v>783</v>
-      </c>
-      <c r="I46" s="233" t="s">
-        <v>784</v>
-      </c>
-      <c r="J46" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K46" s="251"/>
-      <c r="L46" s="251"/>
-      <c r="M46" s="251"/>
-      <c r="N46" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O46" s="258" t="s">
-        <v>787</v>
-      </c>
-      <c r="P46" s="258" t="n">
-        <v>100170</v>
-      </c>
-      <c r="Q46" s="258" t="s">
-        <v>792</v>
-      </c>
-      <c r="R46" s="258"/>
-      <c r="S46" s="270"/>
-    </row>
-    <row r="47" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="271" t="s">
-        <v>794</v>
-      </c>
-      <c r="B47" s="248" t="s">
-        <v>795</v>
-      </c>
-      <c r="C47" s="276" t="s">
-        <v>780</v>
-      </c>
-      <c r="D47" s="269"/>
-      <c r="E47" s="233" t="s">
-        <v>781</v>
-      </c>
-      <c r="F47" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G47" s="269"/>
-      <c r="H47" s="233" t="s">
-        <v>783</v>
-      </c>
-      <c r="I47" s="233" t="s">
-        <v>784</v>
-      </c>
-      <c r="J47" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K47" s="251"/>
-      <c r="L47" s="251"/>
-      <c r="M47" s="251"/>
-      <c r="N47" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O47" s="258" t="s">
-        <v>796</v>
-      </c>
-      <c r="P47" s="258" t="n">
-        <v>100165</v>
-      </c>
-      <c r="Q47" s="258" t="s">
-        <v>792</v>
-      </c>
-      <c r="R47" s="258"/>
-      <c r="S47" s="270"/>
-    </row>
-    <row r="48" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="258" t="s">
-        <v>797</v>
-      </c>
-      <c r="B48" s="279" t="s">
-        <v>795</v>
-      </c>
-      <c r="C48" s="277" t="s">
-        <v>780</v>
-      </c>
-      <c r="D48" s="269"/>
-      <c r="E48" s="233" t="s">
-        <v>781</v>
-      </c>
-      <c r="F48" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G48" s="269"/>
-      <c r="H48" s="233" t="s">
-        <v>783</v>
-      </c>
-      <c r="I48" s="233" t="s">
-        <v>784</v>
-      </c>
-      <c r="J48" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K48" s="251"/>
-      <c r="L48" s="251"/>
-      <c r="M48" s="251"/>
-      <c r="N48" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O48" s="258" t="s">
-        <v>796</v>
-      </c>
-      <c r="P48" s="258" t="n">
-        <v>100164</v>
-      </c>
-      <c r="Q48" s="258" t="s">
-        <v>792</v>
-      </c>
-      <c r="R48" s="258"/>
-      <c r="S48" s="270"/>
-    </row>
-    <row r="49" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="271" t="s">
-        <v>798</v>
-      </c>
-      <c r="B49" s="248" t="s">
-        <v>799</v>
-      </c>
-      <c r="C49" s="272" t="s">
-        <v>800</v>
-      </c>
-      <c r="D49" s="269"/>
-      <c r="E49" s="233" t="s">
-        <v>801</v>
-      </c>
-      <c r="F49" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G49" s="269"/>
-      <c r="H49" s="233" t="s">
-        <v>802</v>
-      </c>
-      <c r="I49" s="233"/>
-      <c r="J49" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K49" s="251"/>
-      <c r="L49" s="251"/>
-      <c r="M49" s="251"/>
-      <c r="N49" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O49" s="258" t="s">
-        <v>803</v>
-      </c>
-      <c r="P49" s="258" t="s">
-        <v>804</v>
-      </c>
-      <c r="Q49" s="258" t="s">
-        <v>680</v>
-      </c>
-      <c r="R49" s="258"/>
-      <c r="S49" s="270"/>
-    </row>
-    <row r="50" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="280" t="s">
-        <v>805</v>
-      </c>
-      <c r="B50" s="281" t="s">
-        <v>806</v>
-      </c>
-      <c r="C50" s="271" t="s">
-        <v>800</v>
-      </c>
-      <c r="D50" s="269"/>
-      <c r="E50" s="233" t="s">
-        <v>801</v>
-      </c>
-      <c r="F50" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G50" s="269"/>
-      <c r="H50" s="233" t="s">
-        <v>807</v>
-      </c>
-      <c r="I50" s="233" t="s">
-        <v>808</v>
-      </c>
-      <c r="J50" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K50" s="251"/>
-      <c r="L50" s="251"/>
-      <c r="M50" s="251"/>
-      <c r="N50" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O50" s="258" t="s">
-        <v>809</v>
-      </c>
-      <c r="P50" s="258" t="s">
-        <v>810</v>
-      </c>
-      <c r="Q50" s="258" t="s">
-        <v>680</v>
-      </c>
-      <c r="R50" s="258"/>
-      <c r="S50" s="270"/>
-    </row>
-    <row r="51" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="258" t="s">
-        <v>811</v>
-      </c>
-      <c r="B51" s="279" t="s">
-        <v>812</v>
-      </c>
-      <c r="C51" s="272" t="s">
-        <v>800</v>
-      </c>
-      <c r="D51" s="269"/>
-      <c r="E51" s="233" t="s">
-        <v>813</v>
-      </c>
-      <c r="F51" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G51" s="269"/>
-      <c r="H51" s="233" t="s">
-        <v>814</v>
-      </c>
-      <c r="I51" s="233"/>
-      <c r="J51" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K51" s="251"/>
-      <c r="L51" s="251"/>
-      <c r="M51" s="251"/>
-      <c r="N51" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O51" s="258" t="s">
-        <v>815</v>
-      </c>
-      <c r="P51" s="258" t="n">
-        <v>100162</v>
-      </c>
-      <c r="Q51" s="258" t="s">
-        <v>680</v>
-      </c>
-      <c r="R51" s="258"/>
-      <c r="S51" s="270"/>
-    </row>
-    <row r="52" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="271" t="s">
-        <v>816</v>
-      </c>
-      <c r="B52" s="241" t="s">
-        <v>817</v>
-      </c>
-      <c r="C52" s="271" t="s">
-        <v>800</v>
-      </c>
-      <c r="D52" s="269"/>
-      <c r="E52" s="233" t="s">
-        <v>813</v>
-      </c>
-      <c r="F52" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G52" s="269"/>
-      <c r="H52" s="233" t="s">
-        <v>814</v>
-      </c>
-      <c r="I52" s="233" t="s">
-        <v>784</v>
-      </c>
-      <c r="J52" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K52" s="251"/>
-      <c r="L52" s="251"/>
-      <c r="M52" s="251"/>
-      <c r="N52" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O52" s="258" t="s">
-        <v>815</v>
-      </c>
-      <c r="P52" s="258" t="n">
-        <v>100163</v>
-      </c>
-      <c r="Q52" s="258" t="s">
-        <v>680</v>
-      </c>
-      <c r="R52" s="258"/>
-      <c r="S52" s="270"/>
-    </row>
-    <row r="53" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="278" t="s">
-        <v>818</v>
-      </c>
-      <c r="B53" s="248" t="s">
-        <v>819</v>
-      </c>
-      <c r="C53" s="278" t="s">
-        <v>800</v>
-      </c>
-      <c r="D53" s="269"/>
-      <c r="E53" s="233" t="s">
-        <v>801</v>
-      </c>
-      <c r="F53" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G53" s="269"/>
-      <c r="H53" s="233" t="s">
-        <v>807</v>
-      </c>
-      <c r="I53" s="233"/>
-      <c r="J53" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K53" s="251"/>
-      <c r="L53" s="251"/>
-      <c r="M53" s="251"/>
-      <c r="N53" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O53" s="258" t="s">
-        <v>809</v>
-      </c>
-      <c r="P53" s="258" t="s">
-        <v>820</v>
-      </c>
-      <c r="Q53" s="258" t="s">
-        <v>792</v>
-      </c>
-      <c r="R53" s="258"/>
-      <c r="S53" s="270"/>
-    </row>
-    <row r="54" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="278" t="s">
-        <v>821</v>
-      </c>
-      <c r="B54" s="254" t="s">
-        <v>822</v>
-      </c>
-      <c r="C54" s="272" t="s">
-        <v>800</v>
-      </c>
-      <c r="D54" s="269"/>
-      <c r="E54" s="233" t="s">
-        <v>801</v>
-      </c>
-      <c r="F54" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G54" s="269"/>
-      <c r="H54" s="233" t="s">
-        <v>807</v>
-      </c>
-      <c r="I54" s="233" t="s">
-        <v>784</v>
-      </c>
-      <c r="J54" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K54" s="251"/>
-      <c r="L54" s="251"/>
-      <c r="M54" s="251"/>
-      <c r="N54" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O54" s="258" t="s">
-        <v>809</v>
-      </c>
-      <c r="P54" s="258" t="s">
-        <v>823</v>
-      </c>
-      <c r="Q54" s="258" t="s">
-        <v>792</v>
-      </c>
-      <c r="R54" s="258"/>
-      <c r="S54" s="270"/>
-    </row>
-    <row r="55" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="278" t="s">
-        <v>824</v>
-      </c>
-      <c r="B55" s="254" t="s">
-        <v>825</v>
-      </c>
-      <c r="C55" s="271" t="s">
-        <v>800</v>
-      </c>
-      <c r="D55" s="269"/>
-      <c r="E55" s="233" t="s">
-        <v>813</v>
-      </c>
-      <c r="F55" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G55" s="269"/>
-      <c r="H55" s="233" t="s">
-        <v>826</v>
-      </c>
-      <c r="I55" s="233" t="s">
-        <v>827</v>
-      </c>
-      <c r="J55" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K55" s="251"/>
-      <c r="L55" s="251"/>
-      <c r="M55" s="251"/>
-      <c r="N55" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O55" s="258" t="s">
-        <v>828</v>
-      </c>
-      <c r="P55" s="258" t="n">
-        <v>170166</v>
-      </c>
-      <c r="Q55" s="258" t="s">
-        <v>680</v>
-      </c>
-      <c r="R55" s="258"/>
-      <c r="S55" s="270"/>
-    </row>
-    <row r="56" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="280" t="s">
-        <v>829</v>
-      </c>
-      <c r="B56" s="279" t="s">
-        <v>825</v>
-      </c>
-      <c r="C56" s="278" t="s">
-        <v>800</v>
-      </c>
-      <c r="D56" s="269"/>
-      <c r="E56" s="233" t="s">
-        <v>813</v>
-      </c>
-      <c r="F56" s="233" t="s">
-        <v>782</v>
-      </c>
-      <c r="G56" s="269"/>
-      <c r="H56" s="233" t="s">
-        <v>826</v>
-      </c>
-      <c r="I56" s="233" t="s">
-        <v>827</v>
-      </c>
-      <c r="J56" s="233" t="s">
-        <v>785</v>
-      </c>
-      <c r="K56" s="251"/>
-      <c r="L56" s="251"/>
-      <c r="M56" s="251"/>
-      <c r="N56" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O56" s="258" t="s">
-        <v>828</v>
-      </c>
-      <c r="P56" s="258" t="n">
-        <v>170165</v>
-      </c>
-      <c r="Q56" s="258" t="s">
-        <v>680</v>
-      </c>
-      <c r="R56" s="258"/>
-      <c r="S56" s="270"/>
-    </row>
-    <row r="57" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="278" t="s">
-        <v>830</v>
-      </c>
-      <c r="B57" s="248" t="s">
-        <v>831</v>
-      </c>
-      <c r="C57" s="278" t="s">
-        <v>780</v>
-      </c>
-      <c r="D57" s="269"/>
-      <c r="E57" s="233" t="s">
-        <v>832</v>
-      </c>
-      <c r="F57" s="233" t="s">
-        <v>833</v>
-      </c>
-      <c r="G57" s="233" t="s">
-        <v>834</v>
-      </c>
-      <c r="H57" s="233" t="s">
-        <v>835</v>
-      </c>
-      <c r="I57" s="233" t="s">
-        <v>836</v>
-      </c>
-      <c r="J57" s="233"/>
-      <c r="K57" s="269"/>
-      <c r="L57" s="269"/>
-      <c r="M57" s="269"/>
-      <c r="N57" s="237" t="s">
-        <v>786</v>
-      </c>
-      <c r="O57" s="258"/>
-      <c r="P57" s="258" t="n">
-        <v>200505</v>
-      </c>
-      <c r="Q57" s="258" t="s">
-        <v>680</v>
-      </c>
-      <c r="R57" s="258"/>
-      <c r="S57" s="270"/>
-    </row>
-    <row r="58" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="272" t="s">
-        <v>837</v>
-      </c>
-      <c r="B58" s="254" t="s">
-        <v>838</v>
-      </c>
-      <c r="C58" s="274" t="s">
-        <v>780</v>
-      </c>
-      <c r="D58" s="269"/>
-      <c r="E58" s="233" t="s">
-        <v>839</v>
-      </c>
-      <c r="F58" s="233" t="s">
-        <v>840</v>
-      </c>
-      <c r="G58" s="233" t="s">
-        <v>841</v>
-      </c>
-      <c r="H58" s="233" t="s">
-        <v>842</v>
-      </c>
-      <c r="I58" s="233" t="s">
-        <v>843</v>
-      </c>
-      <c r="J58" s="233"/>
-      <c r="K58" s="269"/>
-      <c r="L58" s="269"/>
-      <c r="M58" s="269"/>
-      <c r="N58" s="237" t="s">
-        <v>844</v>
-      </c>
-      <c r="O58" s="258" t="s">
-        <v>845</v>
-      </c>
-      <c r="P58" s="258"/>
-      <c r="Q58" s="258" t="s">
-        <v>680</v>
-      </c>
-      <c r="R58" s="258"/>
-      <c r="S58" s="270"/>
+      <c r="R58" s="253"/>
+      <c r="S58" s="265"/>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="282"/>
-      <c r="B59" s="282"/>
-      <c r="C59" s="282"/>
-      <c r="D59" s="283"/>
-      <c r="E59" s="283"/>
-      <c r="F59" s="283"/>
-      <c r="G59" s="283"/>
-      <c r="H59" s="283"/>
-      <c r="I59" s="283"/>
-      <c r="J59" s="283"/>
-      <c r="K59" s="283"/>
-      <c r="L59" s="283"/>
-      <c r="M59" s="283"/>
-      <c r="N59" s="283"/>
-      <c r="O59" s="283"/>
-      <c r="P59" s="283"/>
-      <c r="Q59" s="283"/>
-      <c r="R59" s="283"/>
+      <c r="A59" s="277"/>
+      <c r="B59" s="277"/>
+      <c r="C59" s="277"/>
+      <c r="D59" s="278"/>
+      <c r="E59" s="278"/>
+      <c r="F59" s="278"/>
+      <c r="G59" s="278"/>
+      <c r="H59" s="278"/>
+      <c r="I59" s="278"/>
+      <c r="J59" s="278"/>
+      <c r="K59" s="278"/>
+      <c r="L59" s="278"/>
+      <c r="M59" s="278"/>
+      <c r="N59" s="278"/>
+      <c r="O59" s="278"/>
+      <c r="P59" s="278"/>
+      <c r="Q59" s="278"/>
+      <c r="R59" s="278"/>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="282"/>
-      <c r="B60" s="282"/>
-      <c r="C60" s="282"/>
-      <c r="D60" s="283"/>
-      <c r="E60" s="283"/>
-      <c r="F60" s="283"/>
-      <c r="G60" s="283"/>
-      <c r="H60" s="283"/>
-      <c r="I60" s="283"/>
-      <c r="J60" s="283"/>
-      <c r="K60" s="283"/>
-      <c r="L60" s="283"/>
-      <c r="M60" s="283"/>
-      <c r="N60" s="283"/>
-      <c r="O60" s="283"/>
-      <c r="P60" s="283"/>
-      <c r="Q60" s="283"/>
-      <c r="R60" s="283"/>
+      <c r="A60" s="277"/>
+      <c r="B60" s="277"/>
+      <c r="C60" s="277"/>
+      <c r="D60" s="278"/>
+      <c r="E60" s="278"/>
+      <c r="F60" s="278"/>
+      <c r="G60" s="278"/>
+      <c r="H60" s="278"/>
+      <c r="I60" s="278"/>
+      <c r="J60" s="278"/>
+      <c r="K60" s="278"/>
+      <c r="L60" s="278"/>
+      <c r="M60" s="278"/>
+      <c r="N60" s="278"/>
+      <c r="O60" s="278"/>
+      <c r="P60" s="278"/>
+      <c r="Q60" s="278"/>
+      <c r="R60" s="278"/>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="282"/>
-      <c r="B61" s="282"/>
-      <c r="C61" s="282"/>
-      <c r="D61" s="283"/>
-      <c r="E61" s="283"/>
-      <c r="F61" s="283"/>
-      <c r="G61" s="283"/>
-      <c r="H61" s="283"/>
-      <c r="I61" s="283"/>
-      <c r="J61" s="283"/>
-      <c r="K61" s="283"/>
-      <c r="L61" s="283"/>
-      <c r="M61" s="283"/>
-      <c r="N61" s="283"/>
-      <c r="O61" s="283"/>
-      <c r="P61" s="283"/>
-      <c r="Q61" s="283"/>
-      <c r="R61" s="283"/>
+      <c r="A61" s="277"/>
+      <c r="B61" s="277"/>
+      <c r="C61" s="277"/>
+      <c r="D61" s="278"/>
+      <c r="E61" s="278"/>
+      <c r="F61" s="278"/>
+      <c r="G61" s="278"/>
+      <c r="H61" s="278"/>
+      <c r="I61" s="278"/>
+      <c r="J61" s="278"/>
+      <c r="K61" s="278"/>
+      <c r="L61" s="278"/>
+      <c r="M61" s="278"/>
+      <c r="N61" s="278"/>
+      <c r="O61" s="278"/>
+      <c r="P61" s="278"/>
+      <c r="Q61" s="278"/>
+      <c r="R61" s="278"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -8617,108 +8594,108 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="144" width="27.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="144" width="31.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="144" width="24.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="144" width="30.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="144" width="52.12"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="144" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="139" width="27.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="139" width="31.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="139" width="24.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="139" width="30.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="139" width="52.12"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="139" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="153" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="284" t="s">
+    <row r="1" s="148" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="279" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="284" t="s">
+      <c r="B1" s="279" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="284" t="s">
+      <c r="C1" s="279" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="284" t="s">
+      <c r="D1" s="279" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="284" t="s">
+      <c r="E1" s="279" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="101.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="285" t="s">
+      <c r="A2" s="280" t="s">
+        <v>845</v>
+      </c>
+      <c r="B2" s="280" t="s">
         <v>846</v>
       </c>
-      <c r="B2" s="285" t="s">
+      <c r="C2" s="281" t="s">
         <v>847</v>
       </c>
-      <c r="C2" s="286" t="s">
+      <c r="D2" s="281"/>
+      <c r="E2" s="282" t="s">
         <v>848</v>
       </c>
-      <c r="D2" s="286"/>
-      <c r="E2" s="287" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="280" t="s">
+        <v>779</v>
+      </c>
+      <c r="B3" s="280" t="s">
         <v>849</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="104.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="285" t="s">
-        <v>780</v>
-      </c>
-      <c r="B3" s="285" t="s">
+      <c r="C3" s="280"/>
+      <c r="D3" s="280"/>
+      <c r="E3" s="282" t="s">
         <v>850</v>
       </c>
-      <c r="C3" s="285"/>
-      <c r="D3" s="285"/>
-      <c r="E3" s="287" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="280" t="s">
+        <v>799</v>
+      </c>
+      <c r="B4" s="280" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="100.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="285" t="s">
-        <v>800</v>
-      </c>
-      <c r="B4" s="285" t="s">
+      <c r="C4" s="281" t="s">
         <v>852</v>
       </c>
-      <c r="C4" s="286" t="s">
+      <c r="D4" s="281" t="s">
         <v>853</v>
       </c>
-      <c r="D4" s="286" t="s">
+      <c r="E4" s="282" t="s">
         <v>854</v>
       </c>
-      <c r="E4" s="287" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="283" t="s">
         <v>855</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="288" t="s">
+      <c r="B5" s="283" t="s">
         <v>856</v>
       </c>
-      <c r="B5" s="288" t="s">
+      <c r="C5" s="284" t="s">
         <v>857</v>
       </c>
-      <c r="C5" s="289" t="s">
+      <c r="D5" s="283"/>
+      <c r="E5" s="282" t="s">
         <v>858</v>
       </c>
-      <c r="D5" s="288"/>
-      <c r="E5" s="287" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="283" t="s">
         <v>859</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="167.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="288" t="s">
+      <c r="B6" s="283"/>
+      <c r="C6" s="283"/>
+      <c r="D6" s="283"/>
+      <c r="E6" s="282" t="s">
         <v>860</v>
       </c>
-      <c r="B6" s="288"/>
-      <c r="C6" s="288"/>
-      <c r="D6" s="288"/>
-      <c r="E6" s="287" t="s">
-        <v>861</v>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="288"/>
-      <c r="B7" s="288"/>
-      <c r="C7" s="288"/>
-      <c r="D7" s="288"/>
-      <c r="E7" s="288"/>
+      <c r="A7" s="283"/>
+      <c r="B7" s="283"/>
+      <c r="C7" s="283"/>
+      <c r="D7" s="283"/>
+      <c r="E7" s="283"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -12903,23 +12880,23 @@
     <tabColor rgb="FF2A6099"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="9.375" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="18" width="10.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="18" width="12.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="18" width="41.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="18" width="115.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="18" width="20.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="18" width="69.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="18" width="21.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="18" width="43.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="18" width="10.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="74" width="37.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="11" style="19" width="9.37"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="16" style="18" width="9.37"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="17" style="75" width="9.37"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="18" style="18" width="9.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="18" width="20.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="18" width="69.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="18" width="21.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="18" width="43.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="18" width="10.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="74" width="37.5"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14" min="10" style="19" width="9.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="15" style="18" width="9.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="16" style="75" width="9.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="18" style="18" width="9.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16384" style="18" width="9.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12932,26 +12909,23 @@
       <c r="C1" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="77" t="s">
+      <c r="D1" s="76" t="s">
         <v>541</v>
       </c>
       <c r="E1" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="76" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="76" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="76" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="79" t="s">
         <v>542</v>
-      </c>
-      <c r="F1" s="76" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="76" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="79" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12960,20 +12934,19 @@
       </c>
       <c r="B2" s="81"/>
       <c r="C2" s="82"/>
-      <c r="D2" s="83"/>
+      <c r="D2" s="80" t="s">
+        <v>543</v>
+      </c>
       <c r="E2" s="80" t="s">
         <v>544</v>
       </c>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="80"/>
+      <c r="G2" s="83" t="s">
         <v>545</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="84" t="s">
+      <c r="H2" s="80"/>
+      <c r="I2" s="84" t="s">
         <v>546</v>
-      </c>
-      <c r="I2" s="80"/>
-      <c r="J2" s="85" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12982,179 +12955,163 @@
       </c>
       <c r="B3" s="81"/>
       <c r="C3" s="81"/>
-      <c r="D3" s="86"/>
-      <c r="E3" s="87" t="s">
+      <c r="D3" s="85" t="s">
+        <v>547</v>
+      </c>
+      <c r="E3" s="80" t="s">
         <v>548</v>
       </c>
-      <c r="F3" s="80" t="s">
+      <c r="F3" s="80"/>
+      <c r="G3" s="86" t="s">
         <v>549</v>
       </c>
-      <c r="G3" s="80"/>
-      <c r="H3" s="88" t="s">
+      <c r="H3" s="80" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="84" t="s">
         <v>550</v>
-      </c>
-      <c r="I3" s="80" t="s">
-        <v>48</v>
-      </c>
-      <c r="J3" s="85" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="80"/>
       <c r="B4" s="81" t="s">
+        <v>551</v>
+      </c>
+      <c r="C4" s="84"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="87" t="s">
         <v>552</v>
       </c>
-      <c r="C4" s="85"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="89" t="s">
-        <v>553</v>
-      </c>
-      <c r="I4" s="80"/>
-      <c r="J4" s="85"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="84"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="80" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B5" s="80"/>
       <c r="C5" s="80"/>
-      <c r="D5" s="90" t="s">
+      <c r="D5" s="85" t="s">
+        <v>554</v>
+      </c>
+      <c r="E5" s="80" t="s">
         <v>555</v>
       </c>
-      <c r="E5" s="87" t="s">
-        <v>555</v>
-      </c>
-      <c r="F5" s="80" t="s">
+      <c r="F5" s="80"/>
+      <c r="G5" s="80" t="s">
         <v>556</v>
       </c>
-      <c r="G5" s="80"/>
       <c r="H5" s="80" t="s">
+        <v>443</v>
+      </c>
+      <c r="I5" s="84" t="s">
         <v>557</v>
-      </c>
-      <c r="I5" s="80" t="s">
-        <v>443</v>
-      </c>
-      <c r="J5" s="85" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="80" t="s">
+        <v>558</v>
+      </c>
+      <c r="B6" s="81" t="s">
         <v>559</v>
       </c>
-      <c r="B6" s="81" t="s">
+      <c r="C6" s="87" t="s">
         <v>560</v>
       </c>
-      <c r="C6" s="89" t="s">
+      <c r="D6" s="85" t="s">
         <v>561</v>
       </c>
-      <c r="D6" s="91" t="s">
+      <c r="E6" s="80" t="s">
         <v>562</v>
       </c>
-      <c r="E6" s="87" t="s">
-        <v>562</v>
-      </c>
-      <c r="F6" s="80" t="s">
+      <c r="F6" s="80"/>
+      <c r="G6" s="80" t="s">
         <v>563</v>
       </c>
-      <c r="G6" s="80"/>
       <c r="H6" s="80" t="s">
+        <v>443</v>
+      </c>
+      <c r="I6" s="84" t="s">
         <v>564</v>
-      </c>
-      <c r="I6" s="80" t="s">
-        <v>443</v>
-      </c>
-      <c r="J6" s="85" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="80" t="s">
+        <v>565</v>
+      </c>
+      <c r="B7" s="81" t="s">
         <v>566</v>
       </c>
-      <c r="B7" s="81" t="s">
+      <c r="C7" s="87" t="s">
         <v>567</v>
       </c>
-      <c r="C7" s="89" t="s">
+      <c r="D7" s="85" t="s">
         <v>568</v>
       </c>
-      <c r="D7" s="91" t="s">
+      <c r="E7" s="80" t="s">
         <v>569</v>
       </c>
-      <c r="E7" s="87" t="s">
-        <v>569</v>
-      </c>
-      <c r="F7" s="80" t="s">
+      <c r="F7" s="80"/>
+      <c r="G7" s="80" t="s">
         <v>570</v>
       </c>
-      <c r="G7" s="80"/>
       <c r="H7" s="80" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="84" t="s">
         <v>571</v>
-      </c>
-      <c r="I7" s="80" t="s">
-        <v>48</v>
-      </c>
-      <c r="J7" s="85" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="80" t="s">
+        <v>572</v>
+      </c>
+      <c r="B8" s="81" t="s">
         <v>573</v>
       </c>
-      <c r="B8" s="81" t="s">
+      <c r="C8" s="87" t="s">
         <v>574</v>
       </c>
-      <c r="C8" s="89" t="s">
+      <c r="D8" s="85" t="s">
         <v>575</v>
       </c>
-      <c r="D8" s="91" t="s">
+      <c r="E8" s="80" t="s">
         <v>576</v>
       </c>
-      <c r="E8" s="87" t="s">
-        <v>576</v>
-      </c>
-      <c r="F8" s="80" t="s">
+      <c r="F8" s="80"/>
+      <c r="G8" s="80" t="s">
         <v>577</v>
       </c>
-      <c r="G8" s="80"/>
       <c r="H8" s="80" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="84" t="s">
         <v>578</v>
-      </c>
-      <c r="I8" s="80" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="85" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="80"/>
-      <c r="B9" s="85"/>
+      <c r="B9" s="84"/>
       <c r="C9" s="80"/>
-      <c r="D9" s="92"/>
+      <c r="D9" s="80"/>
       <c r="E9" s="80"/>
       <c r="F9" s="80"/>
       <c r="G9" s="80"/>
       <c r="H9" s="80"/>
-      <c r="I9" s="80"/>
-      <c r="J9" s="85"/>
+      <c r="I9" s="84"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="80"/>
       <c r="B10" s="80"/>
-      <c r="C10" s="93"/>
+      <c r="C10" s="88"/>
       <c r="D10" s="80"/>
       <c r="E10" s="80"/>
       <c r="F10" s="80"/>
       <c r="G10" s="80"/>
       <c r="H10" s="80"/>
-      <c r="I10" s="80"/>
-      <c r="J10" s="85"/>
+      <c r="I10" s="84"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="80"/>
@@ -13165,8 +13122,7 @@
       <c r="F11" s="80"/>
       <c r="G11" s="80"/>
       <c r="H11" s="80"/>
-      <c r="I11" s="80"/>
-      <c r="J11" s="85"/>
+      <c r="I11" s="84"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="80"/>
@@ -13177,8 +13133,7 @@
       <c r="F12" s="80"/>
       <c r="G12" s="80"/>
       <c r="H12" s="80"/>
-      <c r="I12" s="80"/>
-      <c r="J12" s="85"/>
+      <c r="I12" s="84"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="80"/>
@@ -13189,8 +13144,7 @@
       <c r="F13" s="80"/>
       <c r="G13" s="80"/>
       <c r="H13" s="80"/>
-      <c r="I13" s="80"/>
-      <c r="J13" s="85"/>
+      <c r="I13" s="84"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="80"/>
@@ -13201,8 +13155,7 @@
       <c r="F14" s="80"/>
       <c r="G14" s="80"/>
       <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="85"/>
+      <c r="I14" s="84"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="80"/>
@@ -13213,8 +13166,7 @@
       <c r="F15" s="80"/>
       <c r="G15" s="80"/>
       <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="85"/>
+      <c r="I15" s="84"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="80"/>
@@ -13225,29 +13177,28 @@
       <c r="F16" s="80"/>
       <c r="G16" s="80"/>
       <c r="H16" s="80"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="85"/>
+      <c r="I16" s="84"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I2:I1008" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H2:H1008" type="list">
       <formula1>$A$2:$A$10001</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" display="http://purl.obolibrary.org/obo/NCBITaxon_33090"/>
-    <hyperlink ref="J2" r:id="rId2" display="https://en.wikipedia.org/wiki/Plantae"/>
-    <hyperlink ref="H3" r:id="rId3" display="http://purl.obolibrary.org/obo/NCBITaxon_4479"/>
-    <hyperlink ref="J3" r:id="rId4" display="https://en.wikipedia.org/wiki/Poaceae"/>
-    <hyperlink ref="H4" r:id="rId5" display="http://purl.obolibrary.org/obo/NCBITaxon_4564"/>
-    <hyperlink ref="J5" r:id="rId6" display="https://en.wikipedia.org/wiki/Wheat"/>
+    <hyperlink ref="G2" r:id="rId1" display="http://purl.obolibrary.org/obo/NCBITaxon_33090"/>
+    <hyperlink ref="I2" r:id="rId2" display="https://en.wikipedia.org/wiki/Plantae"/>
+    <hyperlink ref="G3" r:id="rId3" display="http://purl.obolibrary.org/obo/NCBITaxon_4479"/>
+    <hyperlink ref="I3" r:id="rId4" display="https://en.wikipedia.org/wiki/Poaceae"/>
+    <hyperlink ref="G4" r:id="rId5" display="http://purl.obolibrary.org/obo/NCBITaxon_4564"/>
+    <hyperlink ref="I5" r:id="rId6" display="https://en.wikipedia.org/wiki/Wheat"/>
     <hyperlink ref="C6" r:id="rId7" display="http://purl.obolibrary.org/obo/NCBITaxon_4512"/>
-    <hyperlink ref="J6" r:id="rId8" display="https://en.wikipedia.org/wiki/Barley"/>
+    <hyperlink ref="I6" r:id="rId8" display="https://en.wikipedia.org/wiki/Barley"/>
     <hyperlink ref="C7" r:id="rId9" display="http://purl.obolibrary.org/obo/NCBITaxon_4107"/>
-    <hyperlink ref="J7" r:id="rId10" display="https://en.wikipedia.org/wiki/Tomato"/>
+    <hyperlink ref="I7" r:id="rId10" display="https://en.wikipedia.org/wiki/Tomato"/>
     <hyperlink ref="C8" r:id="rId11" display="http://purl.obolibrary.org/obo/NCBITaxon_3482"/>
-    <hyperlink ref="J8" r:id="rId12" display="https://en.wikipedia.org/wiki/Cannabis_sativa"/>
+    <hyperlink ref="I8" r:id="rId12" display="https://en.wikipedia.org/wiki/Cannabis_sativa"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -13268,54 +13219,54 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="9.375" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="94" width="16.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="94" width="42.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="94" width="29.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="89" width="16.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="89" width="42.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="89" width="29.51"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="4" style="20" width="9.37"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="95" t="s">
+      <c r="B1" s="90" t="s">
+        <v>579</v>
+      </c>
+      <c r="C1" s="90" t="s">
         <v>580</v>
       </c>
-      <c r="C1" s="95" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="89" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="94" t="s">
+      <c r="B2" s="89" t="s">
         <v>582</v>
       </c>
-      <c r="B2" s="94" t="s">
+      <c r="C2" s="89" t="s">
         <v>583</v>
       </c>
-      <c r="C2" s="94" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="89" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="94" t="s">
+      <c r="B3" s="89" t="s">
         <v>585</v>
       </c>
-      <c r="B3" s="94" t="s">
+      <c r="C3" s="89" t="s">
         <v>586</v>
       </c>
-      <c r="C3" s="94" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="89" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="94" t="s">
+      <c r="B4" s="91" t="s">
         <v>588</v>
       </c>
-      <c r="B4" s="96" t="s">
+      <c r="C4" s="91" t="s">
         <v>589</v>
-      </c>
-      <c r="C4" s="96" t="s">
-        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -13351,174 +13302,174 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="20" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="103" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="97" t="s">
+    <row r="1" s="98" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="98" t="s">
+      <c r="B1" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="99" t="s">
+      <c r="C1" s="94" t="s">
+        <v>590</v>
+      </c>
+      <c r="D1" s="95" t="s">
         <v>591</v>
       </c>
-      <c r="D1" s="100" t="s">
+      <c r="E1" s="94" t="s">
         <v>592</v>
       </c>
-      <c r="E1" s="99" t="s">
+      <c r="F1" s="94" t="s">
         <v>593</v>
       </c>
-      <c r="F1" s="99" t="s">
+      <c r="G1" s="96"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+    </row>
+    <row r="2" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="99" t="s">
         <v>594</v>
       </c>
-      <c r="G1" s="101"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-    </row>
-    <row r="2" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="104" t="s">
+      <c r="B2" s="100" t="s">
         <v>595</v>
       </c>
-      <c r="B2" s="105" t="s">
+      <c r="C2" s="101" t="s">
         <v>596</v>
       </c>
-      <c r="C2" s="106" t="s">
+      <c r="D2" s="102" t="s">
         <v>597</v>
       </c>
-      <c r="D2" s="107" t="s">
+      <c r="E2" s="103" t="s">
         <v>598</v>
       </c>
-      <c r="E2" s="108" t="s">
+      <c r="F2" s="104" t="s">
         <v>599</v>
       </c>
-      <c r="F2" s="109" t="s">
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
+    </row>
+    <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="106" t="s">
         <v>600</v>
       </c>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-    </row>
-    <row r="3" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="111" t="s">
+      <c r="B3" s="107" t="s">
         <v>601</v>
       </c>
-      <c r="B3" s="112" t="s">
+      <c r="C3" s="108" t="s">
+        <v>596</v>
+      </c>
+      <c r="D3" s="103" t="s">
         <v>602</v>
       </c>
-      <c r="C3" s="113" t="s">
-        <v>597</v>
-      </c>
-      <c r="D3" s="108" t="s">
+      <c r="E3" s="109" t="s">
         <v>603</v>
       </c>
-      <c r="E3" s="114" t="s">
+      <c r="F3" s="110" t="n">
+        <v>5361</v>
+      </c>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+    </row>
+    <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="111" t="s">
         <v>604</v>
       </c>
-      <c r="F3" s="115" t="n">
-        <v>5361</v>
-      </c>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-    </row>
-    <row r="4" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="116" t="s">
+      <c r="B4" s="111" t="s">
         <v>605</v>
       </c>
-      <c r="B4" s="116" t="s">
+      <c r="C4" s="112" t="s">
         <v>606</v>
       </c>
-      <c r="C4" s="117" t="s">
+      <c r="D4" s="113" t="s">
         <v>607</v>
       </c>
-      <c r="D4" s="118" t="s">
+      <c r="E4" s="114" t="s">
         <v>608</v>
       </c>
-      <c r="E4" s="119" t="s">
+      <c r="F4" s="115" t="s">
         <v>609</v>
       </c>
-      <c r="F4" s="120" t="s">
+      <c r="G4" s="105"/>
+      <c r="I4" s="105"/>
+    </row>
+    <row r="5" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="116" t="s">
         <v>610</v>
       </c>
-      <c r="G4" s="110"/>
-      <c r="I4" s="110"/>
-    </row>
-    <row r="5" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="121" t="s">
+      <c r="B5" s="117" t="s">
         <v>611</v>
       </c>
-      <c r="B5" s="122" t="s">
+      <c r="C5" s="118" t="s">
         <v>612</v>
       </c>
-      <c r="C5" s="123" t="s">
+      <c r="D5" s="119" t="s">
         <v>613</v>
       </c>
-      <c r="D5" s="124" t="s">
+      <c r="E5" s="120" t="s">
         <v>614</v>
       </c>
-      <c r="E5" s="125" t="s">
+      <c r="F5" s="121" t="s">
         <v>615</v>
       </c>
-      <c r="F5" s="126" t="s">
+      <c r="I5" s="105"/>
+      <c r="K5" s="122"/>
+      <c r="L5" s="122"/>
+      <c r="M5" s="122"/>
+    </row>
+    <row r="6" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="116" t="s">
         <v>616</v>
       </c>
-      <c r="I5" s="110"/>
-      <c r="K5" s="127"/>
-      <c r="L5" s="127"/>
-      <c r="M5" s="127"/>
-    </row>
-    <row r="6" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="121" t="s">
+      <c r="B6" s="117" t="s">
+        <v>611</v>
+      </c>
+      <c r="C6" s="118" t="s">
+        <v>612</v>
+      </c>
+      <c r="D6" s="119" t="s">
+        <v>613</v>
+      </c>
+      <c r="E6" s="120" t="s">
+        <v>614</v>
+      </c>
+      <c r="F6" s="121" t="s">
         <v>617</v>
       </c>
-      <c r="B6" s="122" t="s">
+      <c r="I6" s="105"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+    </row>
+    <row r="7" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="116" t="s">
+        <v>618</v>
+      </c>
+      <c r="B7" s="117" t="s">
+        <v>611</v>
+      </c>
+      <c r="C7" s="118" t="s">
         <v>612</v>
       </c>
-      <c r="C6" s="123" t="s">
+      <c r="D7" s="119" t="s">
         <v>613</v>
       </c>
-      <c r="D6" s="124" t="s">
+      <c r="E7" s="120" t="s">
         <v>614</v>
       </c>
-      <c r="E6" s="125" t="s">
-        <v>615</v>
-      </c>
-      <c r="F6" s="126" t="s">
-        <v>618</v>
-      </c>
-      <c r="I6" s="110"/>
-      <c r="K6" s="127"/>
-      <c r="L6" s="127"/>
-      <c r="M6" s="127"/>
-    </row>
-    <row r="7" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="121" t="s">
+      <c r="F7" s="121" t="s">
         <v>619</v>
       </c>
-      <c r="B7" s="122" t="s">
-        <v>612</v>
-      </c>
-      <c r="C7" s="123" t="s">
-        <v>613</v>
-      </c>
-      <c r="D7" s="124" t="s">
-        <v>614</v>
-      </c>
-      <c r="E7" s="125" t="s">
-        <v>615</v>
-      </c>
-      <c r="F7" s="126" t="s">
-        <v>620</v>
-      </c>
-      <c r="I7" s="110"/>
-      <c r="K7" s="127"/>
-      <c r="L7" s="127"/>
-      <c r="M7" s="127"/>
+      <c r="I7" s="105"/>
+      <c r="K7" s="122"/>
+      <c r="L7" s="122"/>
+      <c r="M7" s="122"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="128"/>
-      <c r="D8" s="128"/>
-      <c r="E8" s="128"/>
-      <c r="I8" s="110"/>
+      <c r="C8" s="123"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="123"/>
+      <c r="I8" s="105"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -13546,205 +13497,205 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="20" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="130" customFormat="true" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="129" t="s">
+    <row r="1" s="125" customFormat="true" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="124" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="129" t="s">
+      <c r="B1" s="124" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="129" t="s">
+      <c r="C1" s="124" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="129" t="s">
+      <c r="D1" s="124" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="2" s="129" customFormat="true" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="126" t="s">
+        <v>596</v>
+      </c>
+      <c r="B2" s="126" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="2" s="134" customFormat="true" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="131" t="s">
-        <v>597</v>
-      </c>
-      <c r="B2" s="131" t="s">
+      <c r="C2" s="127" t="s">
         <v>622</v>
       </c>
-      <c r="C2" s="132" t="s">
+      <c r="D2" s="128" t="s">
         <v>623</v>
       </c>
-      <c r="D2" s="133" t="s">
+    </row>
+    <row r="3" s="129" customFormat="true" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="130" t="s">
+        <v>606</v>
+      </c>
+      <c r="B3" s="130" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="3" s="134" customFormat="true" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="135" t="s">
-        <v>607</v>
-      </c>
-      <c r="B3" s="135" t="s">
+      <c r="C3" s="131" t="s">
         <v>625</v>
       </c>
-      <c r="C3" s="136" t="s">
+      <c r="D3" s="132" t="s">
         <v>626</v>
       </c>
-      <c r="D3" s="137" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="133" t="s">
+        <v>612</v>
+      </c>
+      <c r="B4" s="134" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="138" t="s">
-        <v>613</v>
-      </c>
-      <c r="B4" s="139" t="s">
+      <c r="C4" s="135" t="s">
         <v>628</v>
       </c>
-      <c r="C4" s="140" t="s">
+      <c r="D4" s="136" t="s">
         <v>629</v>
       </c>
-      <c r="D4" s="141" t="s">
-        <v>630</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="142"/>
-      <c r="B5" s="143"/>
-      <c r="C5" s="143"/>
-      <c r="D5" s="143"/>
+      <c r="A5" s="137"/>
+      <c r="B5" s="138"/>
+      <c r="C5" s="138"/>
+      <c r="D5" s="138"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="143"/>
-      <c r="B6" s="143"/>
-      <c r="C6" s="143"/>
-      <c r="D6" s="143"/>
+      <c r="A6" s="138"/>
+      <c r="B6" s="138"/>
+      <c r="C6" s="138"/>
+      <c r="D6" s="138"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="143"/>
-      <c r="B7" s="143"/>
-      <c r="C7" s="143"/>
-      <c r="D7" s="143"/>
+      <c r="A7" s="138"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="143"/>
-      <c r="B8" s="143"/>
-      <c r="C8" s="143"/>
-      <c r="D8" s="143"/>
+      <c r="A8" s="138"/>
+      <c r="B8" s="138"/>
+      <c r="C8" s="138"/>
+      <c r="D8" s="138"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="143"/>
-      <c r="B9" s="143"/>
-      <c r="C9" s="143"/>
-      <c r="D9" s="143"/>
+      <c r="A9" s="138"/>
+      <c r="B9" s="138"/>
+      <c r="C9" s="138"/>
+      <c r="D9" s="138"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="143"/>
-      <c r="B10" s="143"/>
-      <c r="C10" s="143"/>
-      <c r="D10" s="143"/>
+      <c r="A10" s="138"/>
+      <c r="B10" s="138"/>
+      <c r="C10" s="138"/>
+      <c r="D10" s="138"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="143"/>
-      <c r="B11" s="143"/>
-      <c r="C11" s="143"/>
-      <c r="D11" s="143"/>
+      <c r="A11" s="138"/>
+      <c r="B11" s="138"/>
+      <c r="C11" s="138"/>
+      <c r="D11" s="138"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="143"/>
-      <c r="B12" s="143"/>
-      <c r="C12" s="143"/>
-      <c r="D12" s="143"/>
+      <c r="A12" s="138"/>
+      <c r="B12" s="138"/>
+      <c r="C12" s="138"/>
+      <c r="D12" s="138"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="143"/>
-      <c r="B13" s="143"/>
-      <c r="C13" s="143"/>
-      <c r="D13" s="143"/>
+      <c r="A13" s="138"/>
+      <c r="B13" s="138"/>
+      <c r="C13" s="138"/>
+      <c r="D13" s="138"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="143"/>
-      <c r="B14" s="143"/>
-      <c r="C14" s="143"/>
-      <c r="D14" s="143"/>
+      <c r="A14" s="138"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="143"/>
-      <c r="B15" s="143"/>
-      <c r="C15" s="143"/>
-      <c r="D15" s="143"/>
+      <c r="A15" s="138"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="138"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="143"/>
-      <c r="B16" s="143"/>
-      <c r="C16" s="143"/>
-      <c r="D16" s="143"/>
+      <c r="A16" s="138"/>
+      <c r="B16" s="138"/>
+      <c r="C16" s="138"/>
+      <c r="D16" s="138"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="143"/>
-      <c r="B17" s="143"/>
-      <c r="C17" s="143"/>
-      <c r="D17" s="143"/>
+      <c r="A17" s="138"/>
+      <c r="B17" s="138"/>
+      <c r="C17" s="138"/>
+      <c r="D17" s="138"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="143"/>
-      <c r="B18" s="143"/>
-      <c r="C18" s="143"/>
-      <c r="D18" s="143"/>
+      <c r="A18" s="138"/>
+      <c r="B18" s="138"/>
+      <c r="C18" s="138"/>
+      <c r="D18" s="138"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="143"/>
-      <c r="B19" s="143"/>
-      <c r="C19" s="143"/>
-      <c r="D19" s="143"/>
+      <c r="A19" s="138"/>
+      <c r="B19" s="138"/>
+      <c r="C19" s="138"/>
+      <c r="D19" s="138"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="143"/>
-      <c r="B20" s="143"/>
-      <c r="C20" s="143"/>
-      <c r="D20" s="143"/>
+      <c r="A20" s="138"/>
+      <c r="B20" s="138"/>
+      <c r="C20" s="138"/>
+      <c r="D20" s="138"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="143"/>
-      <c r="B21" s="143"/>
-      <c r="C21" s="143"/>
-      <c r="D21" s="143"/>
+      <c r="A21" s="138"/>
+      <c r="B21" s="138"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="138"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="143"/>
-      <c r="B22" s="143"/>
-      <c r="C22" s="143"/>
-      <c r="D22" s="143"/>
+      <c r="A22" s="138"/>
+      <c r="B22" s="138"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="138"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="143"/>
-      <c r="B23" s="143"/>
-      <c r="C23" s="143"/>
-      <c r="D23" s="143"/>
+      <c r="A23" s="138"/>
+      <c r="B23" s="138"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="138"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="143"/>
-      <c r="B24" s="143"/>
-      <c r="C24" s="143"/>
-      <c r="D24" s="143"/>
+      <c r="A24" s="138"/>
+      <c r="B24" s="138"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="138"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="143"/>
-      <c r="B25" s="143"/>
-      <c r="C25" s="143"/>
-      <c r="D25" s="143"/>
+      <c r="A25" s="138"/>
+      <c r="B25" s="138"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="138"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="143"/>
-      <c r="B26" s="143"/>
-      <c r="C26" s="143"/>
-      <c r="D26" s="143"/>
+      <c r="A26" s="138"/>
+      <c r="B26" s="138"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="143"/>
-      <c r="B27" s="143"/>
-      <c r="C27" s="143"/>
-      <c r="D27" s="143"/>
+      <c r="A27" s="138"/>
+      <c r="B27" s="138"/>
+      <c r="C27" s="138"/>
+      <c r="D27" s="138"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="143"/>
-      <c r="B28" s="143"/>
-      <c r="C28" s="143"/>
-      <c r="D28" s="143"/>
+      <c r="A28" s="138"/>
+      <c r="B28" s="138"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="138"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -13771,430 +13722,430 @@
   <dimension ref="A1:BX18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="144" width="21.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="144" width="34.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="144" width="36.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="144" width="29.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="144" width="16.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="144" width="26.12"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="144" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="139" width="21.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="139" width="34.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="139" width="36.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="139" width="29.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="139" width="16.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="139" width="26.12"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="139" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="153" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="145" t="s">
+    <row r="1" s="148" customFormat="true" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="140" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="146" t="s">
+      <c r="B1" s="141" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="142" t="s">
+        <v>630</v>
+      </c>
+      <c r="D1" s="143" t="s">
         <v>631</v>
       </c>
-      <c r="D1" s="148" t="s">
+      <c r="E1" s="144" t="s">
+        <v>591</v>
+      </c>
+      <c r="F1" s="145" t="s">
+        <v>592</v>
+      </c>
+      <c r="G1" s="141" t="s">
+        <v>593</v>
+      </c>
+      <c r="H1" s="146"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+    </row>
+    <row r="2" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="149" t="s">
+        <v>594</v>
+      </c>
+      <c r="B2" s="150" t="s">
         <v>632</v>
       </c>
-      <c r="E1" s="149" t="s">
-        <v>592</v>
-      </c>
-      <c r="F1" s="150" t="s">
-        <v>593</v>
-      </c>
-      <c r="G1" s="146" t="s">
-        <v>594</v>
-      </c>
-      <c r="H1" s="151"/>
-      <c r="I1" s="152"/>
-      <c r="J1" s="152"/>
-      <c r="K1" s="152"/>
-      <c r="L1" s="152"/>
-    </row>
-    <row r="2" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="154" t="s">
-        <v>595</v>
-      </c>
-      <c r="B2" s="155" t="s">
+      <c r="C2" s="151" t="s">
         <v>633</v>
       </c>
-      <c r="C2" s="156" t="s">
+      <c r="D2" s="152" t="s">
         <v>634</v>
       </c>
-      <c r="D2" s="157" t="s">
+      <c r="E2" s="153" t="s">
+        <v>597</v>
+      </c>
+      <c r="F2" s="154" t="s">
+        <v>598</v>
+      </c>
+      <c r="G2" s="154" t="s">
+        <v>599</v>
+      </c>
+      <c r="H2" s="155"/>
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="155"/>
+    </row>
+    <row r="3" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="156" t="s">
         <v>635</v>
       </c>
-      <c r="E2" s="158" t="s">
-        <v>598</v>
-      </c>
-      <c r="F2" s="159" t="s">
-        <v>599</v>
-      </c>
-      <c r="G2" s="159" t="s">
-        <v>600</v>
-      </c>
-      <c r="H2" s="160"/>
-      <c r="I2" s="160"/>
-      <c r="J2" s="160"/>
-      <c r="K2" s="160"/>
-      <c r="L2" s="160"/>
-    </row>
-    <row r="3" customFormat="false" ht="50.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="161" t="s">
+      <c r="B3" s="157" t="s">
         <v>636</v>
       </c>
-      <c r="B3" s="162" t="s">
+      <c r="C3" s="158" t="s">
         <v>637</v>
       </c>
-      <c r="C3" s="163" t="s">
+      <c r="D3" s="159" t="s">
         <v>638</v>
       </c>
-      <c r="D3" s="164" t="s">
+      <c r="E3" s="160" t="s">
         <v>639</v>
       </c>
-      <c r="E3" s="165" t="s">
+      <c r="F3" s="161" t="s">
         <v>640</v>
       </c>
-      <c r="F3" s="166" t="s">
+      <c r="G3" s="162" t="s">
         <v>641</v>
       </c>
-      <c r="G3" s="167" t="s">
+      <c r="H3" s="163"/>
+      <c r="I3" s="163"/>
+      <c r="J3" s="163"/>
+      <c r="K3" s="163"/>
+      <c r="L3" s="163"/>
+    </row>
+    <row r="4" s="171" customFormat="true" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="164" t="s">
         <v>642</v>
       </c>
-      <c r="H3" s="168"/>
-      <c r="I3" s="168"/>
-      <c r="J3" s="168"/>
-      <c r="K3" s="168"/>
-      <c r="L3" s="168"/>
-    </row>
-    <row r="4" s="176" customFormat="true" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="169" t="s">
+      <c r="B4" s="165" t="s">
         <v>643</v>
       </c>
-      <c r="B4" s="170" t="s">
+      <c r="C4" s="166" t="s">
         <v>644</v>
       </c>
-      <c r="C4" s="171" t="s">
+      <c r="D4" s="166"/>
+      <c r="E4" s="167" t="s">
         <v>645</v>
       </c>
-      <c r="D4" s="171"/>
-      <c r="E4" s="172" t="s">
+      <c r="F4" s="168" t="s">
         <v>646</v>
       </c>
-      <c r="F4" s="173" t="s">
+      <c r="G4" s="168" t="n">
+        <v>403816</v>
+      </c>
+      <c r="H4" s="169"/>
+      <c r="I4" s="169"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="169"/>
+      <c r="L4" s="169"/>
+      <c r="M4" s="170"/>
+      <c r="N4" s="170"/>
+      <c r="O4" s="170"/>
+      <c r="P4" s="170"/>
+      <c r="Q4" s="170"/>
+      <c r="R4" s="170"/>
+      <c r="S4" s="170"/>
+      <c r="T4" s="170"/>
+      <c r="U4" s="170"/>
+      <c r="V4" s="170"/>
+      <c r="W4" s="170"/>
+      <c r="X4" s="170"/>
+      <c r="Y4" s="170"/>
+      <c r="Z4" s="170"/>
+      <c r="AA4" s="170"/>
+      <c r="AB4" s="170"/>
+      <c r="AC4" s="170"/>
+      <c r="AD4" s="170"/>
+      <c r="AE4" s="170"/>
+      <c r="AF4" s="170"/>
+      <c r="AG4" s="170"/>
+      <c r="AH4" s="170"/>
+      <c r="AI4" s="170"/>
+      <c r="AJ4" s="170"/>
+      <c r="AK4" s="170"/>
+      <c r="AL4" s="170"/>
+      <c r="AM4" s="170"/>
+      <c r="AN4" s="170"/>
+      <c r="AO4" s="170"/>
+      <c r="AP4" s="170"/>
+      <c r="AQ4" s="170"/>
+      <c r="AR4" s="170"/>
+      <c r="AS4" s="170"/>
+      <c r="AT4" s="170"/>
+      <c r="AU4" s="170"/>
+      <c r="AV4" s="170"/>
+      <c r="AW4" s="170"/>
+      <c r="AX4" s="170"/>
+      <c r="AY4" s="170"/>
+      <c r="AZ4" s="170"/>
+      <c r="BA4" s="170"/>
+      <c r="BB4" s="170"/>
+      <c r="BC4" s="170"/>
+      <c r="BD4" s="170"/>
+      <c r="BE4" s="170"/>
+      <c r="BF4" s="170"/>
+      <c r="BG4" s="170"/>
+      <c r="BH4" s="170"/>
+      <c r="BI4" s="170"/>
+      <c r="BJ4" s="170"/>
+      <c r="BK4" s="170"/>
+      <c r="BL4" s="170"/>
+      <c r="BM4" s="170"/>
+      <c r="BN4" s="170"/>
+      <c r="BO4" s="170"/>
+      <c r="BP4" s="170"/>
+      <c r="BQ4" s="170"/>
+      <c r="BR4" s="170"/>
+      <c r="BS4" s="170"/>
+      <c r="BT4" s="170"/>
+      <c r="BU4" s="170"/>
+      <c r="BV4" s="170"/>
+      <c r="BW4" s="170"/>
+      <c r="BX4" s="170"/>
+    </row>
+    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="172" t="s">
         <v>647</v>
       </c>
-      <c r="G4" s="173" t="n">
-        <v>403816</v>
-      </c>
-      <c r="H4" s="174"/>
-      <c r="I4" s="174"/>
-      <c r="J4" s="174"/>
-      <c r="K4" s="174"/>
-      <c r="L4" s="174"/>
-      <c r="M4" s="175"/>
-      <c r="N4" s="175"/>
-      <c r="O4" s="175"/>
-      <c r="P4" s="175"/>
-      <c r="Q4" s="175"/>
-      <c r="R4" s="175"/>
-      <c r="S4" s="175"/>
-      <c r="T4" s="175"/>
-      <c r="U4" s="175"/>
-      <c r="V4" s="175"/>
-      <c r="W4" s="175"/>
-      <c r="X4" s="175"/>
-      <c r="Y4" s="175"/>
-      <c r="Z4" s="175"/>
-      <c r="AA4" s="175"/>
-      <c r="AB4" s="175"/>
-      <c r="AC4" s="175"/>
-      <c r="AD4" s="175"/>
-      <c r="AE4" s="175"/>
-      <c r="AF4" s="175"/>
-      <c r="AG4" s="175"/>
-      <c r="AH4" s="175"/>
-      <c r="AI4" s="175"/>
-      <c r="AJ4" s="175"/>
-      <c r="AK4" s="175"/>
-      <c r="AL4" s="175"/>
-      <c r="AM4" s="175"/>
-      <c r="AN4" s="175"/>
-      <c r="AO4" s="175"/>
-      <c r="AP4" s="175"/>
-      <c r="AQ4" s="175"/>
-      <c r="AR4" s="175"/>
-      <c r="AS4" s="175"/>
-      <c r="AT4" s="175"/>
-      <c r="AU4" s="175"/>
-      <c r="AV4" s="175"/>
-      <c r="AW4" s="175"/>
-      <c r="AX4" s="175"/>
-      <c r="AY4" s="175"/>
-      <c r="AZ4" s="175"/>
-      <c r="BA4" s="175"/>
-      <c r="BB4" s="175"/>
-      <c r="BC4" s="175"/>
-      <c r="BD4" s="175"/>
-      <c r="BE4" s="175"/>
-      <c r="BF4" s="175"/>
-      <c r="BG4" s="175"/>
-      <c r="BH4" s="175"/>
-      <c r="BI4" s="175"/>
-      <c r="BJ4" s="175"/>
-      <c r="BK4" s="175"/>
-      <c r="BL4" s="175"/>
-      <c r="BM4" s="175"/>
-      <c r="BN4" s="175"/>
-      <c r="BO4" s="175"/>
-      <c r="BP4" s="175"/>
-      <c r="BQ4" s="175"/>
-      <c r="BR4" s="175"/>
-      <c r="BS4" s="175"/>
-      <c r="BT4" s="175"/>
-      <c r="BU4" s="175"/>
-      <c r="BV4" s="175"/>
-      <c r="BW4" s="175"/>
-      <c r="BX4" s="175"/>
-    </row>
-    <row r="5" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="177" t="s">
+      <c r="B5" s="173" t="s">
         <v>648</v>
       </c>
-      <c r="B5" s="178" t="s">
+      <c r="C5" s="174" t="s">
         <v>649</v>
       </c>
-      <c r="C5" s="179" t="s">
+      <c r="D5" s="172"/>
+      <c r="E5" s="175" t="s">
+        <v>613</v>
+      </c>
+      <c r="F5" s="167"/>
+      <c r="G5" s="176" t="s">
+        <v>615</v>
+      </c>
+      <c r="H5" s="177"/>
+      <c r="I5" s="178"/>
+      <c r="J5" s="178"/>
+      <c r="K5" s="179"/>
+      <c r="L5" s="178"/>
+      <c r="M5" s="180"/>
+      <c r="N5" s="180"/>
+      <c r="O5" s="180"/>
+      <c r="P5" s="180"/>
+      <c r="Q5" s="180"/>
+      <c r="R5" s="180"/>
+      <c r="S5" s="181"/>
+      <c r="T5" s="171"/>
+      <c r="U5" s="171"/>
+      <c r="V5" s="171"/>
+      <c r="W5" s="171"/>
+      <c r="X5" s="171"/>
+      <c r="Y5" s="171"/>
+      <c r="Z5" s="171"/>
+      <c r="AA5" s="171"/>
+      <c r="AB5" s="171"/>
+      <c r="AC5" s="171"/>
+      <c r="AD5" s="171"/>
+      <c r="AE5" s="171"/>
+      <c r="AF5" s="171"/>
+      <c r="AG5" s="171"/>
+      <c r="AH5" s="171"/>
+      <c r="AI5" s="171"/>
+      <c r="AJ5" s="171"/>
+      <c r="AK5" s="171"/>
+      <c r="AL5" s="171"/>
+      <c r="AM5" s="171"/>
+      <c r="AN5" s="171"/>
+      <c r="AO5" s="171"/>
+      <c r="AP5" s="171"/>
+      <c r="AQ5" s="171"/>
+      <c r="AR5" s="171"/>
+      <c r="AS5" s="171"/>
+      <c r="AT5" s="171"/>
+      <c r="AU5" s="171"/>
+      <c r="AV5" s="171"/>
+      <c r="AW5" s="171"/>
+      <c r="AX5" s="171"/>
+      <c r="AY5" s="171"/>
+      <c r="AZ5" s="171"/>
+      <c r="BA5" s="171"/>
+      <c r="BB5" s="171"/>
+      <c r="BC5" s="171"/>
+      <c r="BD5" s="171"/>
+      <c r="BE5" s="171"/>
+      <c r="BF5" s="171"/>
+      <c r="BG5" s="171"/>
+      <c r="BH5" s="171"/>
+      <c r="BI5" s="171"/>
+      <c r="BJ5" s="171"/>
+      <c r="BK5" s="171"/>
+      <c r="BL5" s="171"/>
+      <c r="BM5" s="171"/>
+      <c r="BN5" s="171"/>
+      <c r="BO5" s="171"/>
+      <c r="BP5" s="171"/>
+      <c r="BQ5" s="171"/>
+      <c r="BR5" s="171"/>
+      <c r="BS5" s="171"/>
+      <c r="BT5" s="171"/>
+      <c r="BU5" s="171"/>
+      <c r="BV5" s="171"/>
+      <c r="BW5" s="171"/>
+      <c r="BX5" s="171"/>
+    </row>
+    <row r="6" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="172" t="s">
         <v>650</v>
       </c>
-      <c r="D5" s="177"/>
-      <c r="E5" s="180" t="s">
-        <v>614</v>
-      </c>
-      <c r="F5" s="172"/>
-      <c r="G5" s="181" t="s">
-        <v>616</v>
-      </c>
-      <c r="H5" s="182"/>
-      <c r="I5" s="183"/>
-      <c r="J5" s="183"/>
-      <c r="K5" s="184"/>
-      <c r="L5" s="183"/>
-      <c r="M5" s="185"/>
-      <c r="N5" s="185"/>
-      <c r="O5" s="185"/>
-      <c r="P5" s="185"/>
-      <c r="Q5" s="185"/>
-      <c r="R5" s="185"/>
-      <c r="S5" s="186"/>
-      <c r="T5" s="176"/>
-      <c r="U5" s="176"/>
-      <c r="V5" s="176"/>
-      <c r="W5" s="176"/>
-      <c r="X5" s="176"/>
-      <c r="Y5" s="176"/>
-      <c r="Z5" s="176"/>
-      <c r="AA5" s="176"/>
-      <c r="AB5" s="176"/>
-      <c r="AC5" s="176"/>
-      <c r="AD5" s="176"/>
-      <c r="AE5" s="176"/>
-      <c r="AF5" s="176"/>
-      <c r="AG5" s="176"/>
-      <c r="AH5" s="176"/>
-      <c r="AI5" s="176"/>
-      <c r="AJ5" s="176"/>
-      <c r="AK5" s="176"/>
-      <c r="AL5" s="176"/>
-      <c r="AM5" s="176"/>
-      <c r="AN5" s="176"/>
-      <c r="AO5" s="176"/>
-      <c r="AP5" s="176"/>
-      <c r="AQ5" s="176"/>
-      <c r="AR5" s="176"/>
-      <c r="AS5" s="176"/>
-      <c r="AT5" s="176"/>
-      <c r="AU5" s="176"/>
-      <c r="AV5" s="176"/>
-      <c r="AW5" s="176"/>
-      <c r="AX5" s="176"/>
-      <c r="AY5" s="176"/>
-      <c r="AZ5" s="176"/>
-      <c r="BA5" s="176"/>
-      <c r="BB5" s="176"/>
-      <c r="BC5" s="176"/>
-      <c r="BD5" s="176"/>
-      <c r="BE5" s="176"/>
-      <c r="BF5" s="176"/>
-      <c r="BG5" s="176"/>
-      <c r="BH5" s="176"/>
-      <c r="BI5" s="176"/>
-      <c r="BJ5" s="176"/>
-      <c r="BK5" s="176"/>
-      <c r="BL5" s="176"/>
-      <c r="BM5" s="176"/>
-      <c r="BN5" s="176"/>
-      <c r="BO5" s="176"/>
-      <c r="BP5" s="176"/>
-      <c r="BQ5" s="176"/>
-      <c r="BR5" s="176"/>
-      <c r="BS5" s="176"/>
-      <c r="BT5" s="176"/>
-      <c r="BU5" s="176"/>
-      <c r="BV5" s="176"/>
-      <c r="BW5" s="176"/>
-      <c r="BX5" s="176"/>
-    </row>
-    <row r="6" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="177" t="s">
+      <c r="B6" s="173" t="s">
+        <v>648</v>
+      </c>
+      <c r="C6" s="174" t="s">
+        <v>649</v>
+      </c>
+      <c r="D6" s="172"/>
+      <c r="E6" s="175" t="s">
+        <v>613</v>
+      </c>
+      <c r="F6" s="167"/>
+      <c r="G6" s="176" t="s">
+        <v>617</v>
+      </c>
+      <c r="H6" s="163"/>
+      <c r="I6" s="163"/>
+      <c r="J6" s="163"/>
+      <c r="K6" s="163"/>
+      <c r="L6" s="163"/>
+      <c r="U6" s="171"/>
+      <c r="V6" s="171"/>
+      <c r="W6" s="171"/>
+      <c r="X6" s="171"/>
+      <c r="Y6" s="171"/>
+      <c r="Z6" s="171"/>
+      <c r="AA6" s="171"/>
+    </row>
+    <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="172" t="s">
         <v>651</v>
       </c>
-      <c r="B6" s="178" t="s">
+      <c r="B7" s="173" t="s">
+        <v>648</v>
+      </c>
+      <c r="C7" s="174" t="s">
         <v>649</v>
       </c>
-      <c r="C6" s="179" t="s">
-        <v>650</v>
-      </c>
-      <c r="D6" s="177"/>
-      <c r="E6" s="180" t="s">
-        <v>614</v>
-      </c>
-      <c r="F6" s="172"/>
-      <c r="G6" s="181" t="s">
-        <v>618</v>
-      </c>
-      <c r="H6" s="168"/>
-      <c r="I6" s="168"/>
-      <c r="J6" s="168"/>
-      <c r="K6" s="168"/>
-      <c r="L6" s="168"/>
-      <c r="U6" s="176"/>
-      <c r="V6" s="176"/>
-      <c r="W6" s="176"/>
-      <c r="X6" s="176"/>
-      <c r="Y6" s="176"/>
-      <c r="Z6" s="176"/>
-      <c r="AA6" s="176"/>
-    </row>
-    <row r="7" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="177" t="s">
-        <v>652</v>
-      </c>
-      <c r="B7" s="178" t="s">
-        <v>649</v>
-      </c>
-      <c r="C7" s="179" t="s">
-        <v>650</v>
-      </c>
-      <c r="D7" s="177"/>
-      <c r="E7" s="180" t="s">
-        <v>614</v>
-      </c>
-      <c r="F7" s="172"/>
-      <c r="G7" s="181" t="s">
-        <v>620</v>
-      </c>
-      <c r="H7" s="168"/>
-      <c r="I7" s="168"/>
-      <c r="J7" s="168"/>
-      <c r="K7" s="168"/>
-      <c r="L7" s="168"/>
+      <c r="D7" s="172"/>
+      <c r="E7" s="175" t="s">
+        <v>613</v>
+      </c>
+      <c r="F7" s="167"/>
+      <c r="G7" s="176" t="s">
+        <v>619</v>
+      </c>
+      <c r="H7" s="163"/>
+      <c r="I7" s="163"/>
+      <c r="J7" s="163"/>
+      <c r="K7" s="163"/>
+      <c r="L7" s="163"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="180"/>
-      <c r="B8" s="187"/>
-      <c r="C8" s="180"/>
-      <c r="D8" s="188"/>
-      <c r="E8" s="180"/>
-      <c r="F8" s="180"/>
-      <c r="G8" s="180"/>
+      <c r="A8" s="175"/>
+      <c r="B8" s="182"/>
+      <c r="C8" s="175"/>
+      <c r="D8" s="183"/>
+      <c r="E8" s="175"/>
+      <c r="F8" s="175"/>
+      <c r="G8" s="175"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="180"/>
-      <c r="B9" s="180"/>
-      <c r="C9" s="180"/>
-      <c r="D9" s="188"/>
-      <c r="E9" s="180"/>
-      <c r="F9" s="180"/>
-      <c r="G9" s="180"/>
+      <c r="A9" s="175"/>
+      <c r="B9" s="175"/>
+      <c r="C9" s="175"/>
+      <c r="D9" s="183"/>
+      <c r="E9" s="175"/>
+      <c r="F9" s="175"/>
+      <c r="G9" s="175"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="180"/>
-      <c r="B10" s="180"/>
-      <c r="C10" s="180"/>
-      <c r="D10" s="180"/>
-      <c r="E10" s="187"/>
-      <c r="F10" s="187"/>
-      <c r="G10" s="187"/>
+      <c r="A10" s="175"/>
+      <c r="B10" s="175"/>
+      <c r="C10" s="175"/>
+      <c r="D10" s="175"/>
+      <c r="E10" s="182"/>
+      <c r="F10" s="182"/>
+      <c r="G10" s="182"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="180"/>
-      <c r="B11" s="180"/>
-      <c r="C11" s="180"/>
-      <c r="D11" s="180"/>
-      <c r="E11" s="180"/>
-      <c r="F11" s="180"/>
-      <c r="G11" s="180"/>
+      <c r="A11" s="175"/>
+      <c r="B11" s="175"/>
+      <c r="C11" s="175"/>
+      <c r="D11" s="175"/>
+      <c r="E11" s="175"/>
+      <c r="F11" s="175"/>
+      <c r="G11" s="175"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="180"/>
-      <c r="B12" s="180"/>
-      <c r="C12" s="180"/>
-      <c r="D12" s="180"/>
-      <c r="E12" s="180"/>
-      <c r="F12" s="180"/>
-      <c r="G12" s="180"/>
+      <c r="A12" s="175"/>
+      <c r="B12" s="175"/>
+      <c r="C12" s="175"/>
+      <c r="D12" s="175"/>
+      <c r="E12" s="175"/>
+      <c r="F12" s="175"/>
+      <c r="G12" s="175"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="180"/>
-      <c r="B13" s="180"/>
-      <c r="C13" s="180"/>
-      <c r="D13" s="180"/>
-      <c r="E13" s="180"/>
-      <c r="F13" s="180"/>
-      <c r="G13" s="180"/>
+      <c r="A13" s="175"/>
+      <c r="B13" s="175"/>
+      <c r="C13" s="175"/>
+      <c r="D13" s="175"/>
+      <c r="E13" s="175"/>
+      <c r="F13" s="175"/>
+      <c r="G13" s="175"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="180"/>
-      <c r="B14" s="180"/>
-      <c r="C14" s="180"/>
-      <c r="D14" s="180"/>
-      <c r="E14" s="180"/>
-      <c r="F14" s="180"/>
-      <c r="G14" s="180"/>
+      <c r="A14" s="175"/>
+      <c r="B14" s="175"/>
+      <c r="C14" s="175"/>
+      <c r="D14" s="175"/>
+      <c r="E14" s="175"/>
+      <c r="F14" s="175"/>
+      <c r="G14" s="175"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="180"/>
-      <c r="B15" s="180"/>
-      <c r="C15" s="180"/>
-      <c r="D15" s="180"/>
-      <c r="E15" s="180"/>
-      <c r="F15" s="180"/>
-      <c r="G15" s="180"/>
+      <c r="A15" s="175"/>
+      <c r="B15" s="175"/>
+      <c r="C15" s="175"/>
+      <c r="D15" s="175"/>
+      <c r="E15" s="175"/>
+      <c r="F15" s="175"/>
+      <c r="G15" s="175"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="180"/>
-      <c r="B16" s="180"/>
-      <c r="C16" s="180"/>
-      <c r="D16" s="180"/>
-      <c r="E16" s="180"/>
-      <c r="F16" s="180"/>
-      <c r="G16" s="180"/>
+      <c r="A16" s="175"/>
+      <c r="B16" s="175"/>
+      <c r="C16" s="175"/>
+      <c r="D16" s="175"/>
+      <c r="E16" s="175"/>
+      <c r="F16" s="175"/>
+      <c r="G16" s="175"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="180"/>
-      <c r="B17" s="180"/>
-      <c r="C17" s="180"/>
-      <c r="D17" s="180"/>
-      <c r="E17" s="180"/>
-      <c r="F17" s="180"/>
-      <c r="G17" s="180"/>
+      <c r="A17" s="175"/>
+      <c r="B17" s="175"/>
+      <c r="C17" s="175"/>
+      <c r="D17" s="175"/>
+      <c r="E17" s="175"/>
+      <c r="F17" s="175"/>
+      <c r="G17" s="175"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="180"/>
-      <c r="B18" s="180"/>
-      <c r="C18" s="180"/>
-      <c r="D18" s="180"/>
-      <c r="E18" s="180"/>
-      <c r="F18" s="180"/>
-      <c r="G18" s="180"/>
+      <c r="A18" s="175"/>
+      <c r="B18" s="175"/>
+      <c r="C18" s="175"/>
+      <c r="D18" s="175"/>
+      <c r="E18" s="175"/>
+      <c r="F18" s="175"/>
+      <c r="G18" s="175"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
